--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10980416-8A95-47EB-A610-D09EF77330B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F456702-1E97-4D7C-B8D2-59CC82B97AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="3" activeTab="4" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10900" firstSheet="3" activeTab="4" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,11 +296,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF434343"/>
-      <name val="ＭＳ ゴシック"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -325,7 +334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -335,7 +344,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -913,7 +928,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
@@ -931,13 +946,13 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="str">
+      <c r="H2" t="str">
         <f>F2</f>
         <v>店の扉が開いた</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
@@ -955,13 +970,13 @@
       <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="str">
+      <c r="H3" s="3" t="str">
         <f>F3</f>
         <v>膝が曲がっていて伸ばすと長い</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B4" t="s">
@@ -979,7 +994,7 @@
       <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="I4" t="str">
+      <c r="H4" t="str">
         <f>F4</f>
         <v>ガスト</v>
       </c>
@@ -987,5 +1002,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F456702-1E97-4D7C-B8D2-59CC82B97AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6B3398-8DD5-4AD3-BAE2-5BBB856F8CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10900" firstSheet="3" activeTab="4" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="3" activeTab="4" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -264,6 +264,44 @@
   </si>
   <si>
     <t>ガスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無線通信規格「Bluetooth」の語源となった王様はどこの国の人？</t>
+    <rPh sb="0" eb="4">
+      <t>ムセンツウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キカク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ゴゲン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>オウサマ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デンマーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロシア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フランス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブルガリア</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -334,7 +372,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -342,9 +380,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -890,7 +925,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690150B6-791B-41CB-87CD-167041B46E25}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
@@ -928,7 +963,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
@@ -952,7 +987,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
@@ -970,13 +1005,13 @@
       <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="H3" t="str">
         <f>F3</f>
         <v>膝が曲がっていて伸ばすと長い</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B4" t="s">
@@ -999,9 +1034,33 @@
         <v>ガスト</v>
       </c>
     </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <f>C5</f>
+        <v>デンマーク</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6B3398-8DD5-4AD3-BAE2-5BBB856F8CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F230C4-41A9-46C3-ABA6-25E87BCE0F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="3" activeTab="4" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="138">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -140,71 +140,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>レンジでチンした→クイズに答えた、レースでゴールした→洗濯物が乾いた、地球が回った→？</t>
-    <rPh sb="13" eb="14">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="27" eb="30">
-      <t>センタクモノ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>カワ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>チキュウ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>マワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>広辞苑が生まれた</t>
-    <rPh sb="0" eb="3">
-      <t>コウジエン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>店の駅の改札が開いた</t>
-    <rPh sb="0" eb="1">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>エキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カイサツ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>妥協した</t>
-    <rPh sb="0" eb="2">
-      <t>ダキョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>店の扉が開いた</t>
-    <rPh sb="0" eb="1">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>トビラ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ペンギンの"足の長さ"について、正しいものを選べ！</t>
   </si>
   <si>
@@ -302,6 +237,1034 @@
   </si>
   <si>
     <t>ブルガリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>綿あめを量産できるようにした人であるウィリアムモリソンの職業と言えば</t>
+    <rPh sb="0" eb="1">
+      <t>ワタ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リョウサン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ショクギョウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>菓子職人</t>
+    <rPh sb="0" eb="4">
+      <t>カシショクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械技師</t>
+    <rPh sb="0" eb="4">
+      <t>キカイギシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歯科医</t>
+    <rPh sb="0" eb="3">
+      <t>シカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>化学者</t>
+    <rPh sb="0" eb="3">
+      <t>カガクシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディスカウントストア、ドン・キホーテのピンク色のマスコットキャラクターの名前は？</t>
+    <rPh sb="22" eb="23">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドンペン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドンコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Youtuberであるハネハネは元何のプロゲームプレーヤーか</t>
+    <rPh sb="16" eb="17">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大乱闘スマッシュブラザーズ</t>
+    <rPh sb="0" eb="3">
+      <t>ダイラントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fortnite</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遊戯王</t>
+    <rPh sb="0" eb="3">
+      <t>ユウギオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラッシュロワイヤル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紅白歌合戦の最多出場数を持つ男性歌手は誰でしょう？</t>
+    <rPh sb="0" eb="5">
+      <t>コウハクウタガッセン</t>
+    </rPh>
+    <rPh sb="6" eb="11">
+      <t>サイタシュツジョウスウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ダンセイカシュ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ダレ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北島三郎</t>
+    <rPh sb="0" eb="4">
+      <t>キタジマサブロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郷ひろみ</t>
+    <rPh sb="0" eb="1">
+      <t>ゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>五木ひろし</t>
+    <rPh sb="0" eb="2">
+      <t>イツキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桑田佳祐</t>
+    <rPh sb="0" eb="4">
+      <t>クワタケイスケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>洋菓子のシュークリームのシューとはフランス語で何という意味でしょう</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウガシ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風船</t>
+    <rPh sb="0" eb="2">
+      <t>フウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>泡</t>
+    <rPh sb="0" eb="1">
+      <t>アワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レタス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャベツ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドラゴンクエストシリーズに登場する呪文の中で間違っている物はどれ？</t>
+    <rPh sb="13" eb="15">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジュモン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バギムーチョ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネクロデイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドルオーラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マヒャドデス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専の校是は何か</t>
+    <rPh sb="0" eb="5">
+      <t>キタキュウシュウコウセン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウゼ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>志遠</t>
+    <rPh sb="0" eb="1">
+      <t>ココロザシ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>トオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開拓</t>
+    <rPh sb="0" eb="2">
+      <t>カイタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>想像</t>
+    <rPh sb="0" eb="2">
+      <t>ソウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雄飛</t>
+    <rPh sb="0" eb="1">
+      <t>オス</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「五月蝿い」読みかたは？</t>
+    <rPh sb="1" eb="3">
+      <t>ゴガツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハエ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うっとうしい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うざったい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>じれったい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うるさい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年現在の北九州市の公立高等学校の数は？</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>キタキュウシュウシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウトウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もっとも総賞金の高いJRAのレースはどれか</t>
+    <rPh sb="4" eb="5">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショウキン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有馬記念</t>
+    <rPh sb="0" eb="4">
+      <t>アリマキネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本ダービー</t>
+    <rPh sb="0" eb="2">
+      <t>ニホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天皇賞（春）</t>
+    <rPh sb="0" eb="3">
+      <t>テンノウショウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャパンカップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専は授業１限分何分あるか</t>
+    <rPh sb="0" eb="5">
+      <t>キタキュウシュウコウセン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジュギョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ナンフン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ようかんは、元々何を使った食べ物だったか</t>
+    <rPh sb="6" eb="8">
+      <t>モトモト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小豆と寒天</t>
+    <rPh sb="0" eb="2">
+      <t>アズキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魚のすり身</t>
+    <rPh sb="0" eb="1">
+      <t>サカナ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野菜の煮物</t>
+    <rPh sb="0" eb="2">
+      <t>ヤサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニモノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羊のスープ</t>
+    <rPh sb="0" eb="1">
+      <t>ヒツジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械学習において、モデルが特定データに適応しすぎてしまい、他の道のデータに対して精度が落ちてしまうことを何というか</t>
+    <rPh sb="0" eb="4">
+      <t>キカイガクシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テキオウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ミチ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超学習</t>
+    <rPh sb="0" eb="3">
+      <t>チョウガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>依存学習</t>
+    <rPh sb="0" eb="4">
+      <t>イゾンガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過学習</t>
+    <rPh sb="0" eb="3">
+      <t>カガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>適応学習</t>
+    <rPh sb="0" eb="4">
+      <t>テキオウガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バナナは植物学上どの仲間か</t>
+    <rPh sb="4" eb="8">
+      <t>ショクブツガクジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナカマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木の実</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野菜</t>
+    <rPh sb="0" eb="2">
+      <t>ヤサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナッツ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1日に長針と短針は何回重なるか</t>
+    <rPh sb="1" eb="2">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チョウシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タンシン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ナンカイカサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本初のボウリング場が作られた都道府県はどこか</t>
+    <rPh sb="0" eb="3">
+      <t>ニホンハツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>トドウフケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京都</t>
+    <rPh sb="0" eb="3">
+      <t>トウキョウト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大阪府</t>
+    <rPh sb="0" eb="3">
+      <t>オオサカフ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>香川県</t>
+    <rPh sb="0" eb="3">
+      <t>カガワケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長崎県</t>
+    <rPh sb="0" eb="3">
+      <t>ナガサキケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイケル・ジャクソンの後ろ向きに歩いているように見える動きの事を何というか</t>
+    <rPh sb="11" eb="12">
+      <t>ウシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジュピターウォーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ムーンウォーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バックウォーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>算ウォーク</t>
+    <rPh sb="0" eb="1">
+      <t>サン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーラなどの炭酸ジュースで、シュワシュワした刺激をもたらしている気体は何か</t>
+    <rPh sb="6" eb="8">
+      <t>タンサン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シゲキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>酸素</t>
+    <rPh sb="0" eb="2">
+      <t>サンソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>窒素</t>
+    <rPh sb="0" eb="2">
+      <t>チッソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水素</t>
+    <rPh sb="0" eb="2">
+      <t>スイソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二酸化炭素</t>
+    <rPh sb="0" eb="5">
+      <t>ニサンカタンソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沖縄の県庁所在地は？</t>
+    <rPh sb="0" eb="2">
+      <t>オキナワ</t>
+    </rPh>
+    <rPh sb="3" eb="8">
+      <t>ケンチョウショザイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>那覇市</t>
+    <rPh sb="0" eb="3">
+      <t>ナハシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沖縄</t>
+    <rPh sb="0" eb="2">
+      <t>オキナワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うるま市</t>
+    <rPh sb="3" eb="4">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石垣市</t>
+    <rPh sb="0" eb="3">
+      <t>イシガキシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年現在YOASOBIで最も多くYoutubeの再生回数が多い曲は？</t>
+    <rPh sb="4" eb="7">
+      <t>ネンゲンザイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>サイセイカイスウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>キョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイドル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜に駆ける</t>
+    <rPh sb="0" eb="1">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>怪物</t>
+    <rPh sb="0" eb="2">
+      <t>カイブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>群青</t>
+    <rPh sb="0" eb="2">
+      <t>グンジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>台形の面積の求め方は？</t>
+    <rPh sb="0" eb="2">
+      <t>ダイケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>メンセキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（上底＋下底）×高さ÷2</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>底辺×高さ÷2</t>
+    <rPh sb="0" eb="2">
+      <t>テイヘン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（上底＋下底）×高さ÷3</t>
+    <rPh sb="1" eb="3">
+      <t>ジョウテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>縦×横</t>
+    <rPh sb="0" eb="2">
+      <t>タテカケル</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「葬送のフリーレン」で主人公のフリーレンが長年旅をともにした勇者の名前は？</t>
+    <rPh sb="1" eb="3">
+      <t>ソウソウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>シュジンコウ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ナガネンタビ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ユウシャ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハイター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイゼン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シュタルク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒンメル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたは、徒競走で2位の選手を追い抜きました。現在何位？</t>
+    <rPh sb="5" eb="8">
+      <t>トキョウソウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センシュ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ゲンザイナンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mhy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数字</t>
+    <rPh sb="0" eb="2">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ある物質の酸素が奪われることを化学的に何というか</t>
+    <rPh sb="2" eb="4">
+      <t>ブッシツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サンソ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウバ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カガク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>逆酸化</t>
+    <rPh sb="0" eb="3">
+      <t>ギャクサンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中化</t>
+    <rPh sb="0" eb="1">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>還元</t>
+    <rPh sb="0" eb="2">
+      <t>カンゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>酸化</t>
+    <rPh sb="0" eb="2">
+      <t>サンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026現在、東海道・山陽新幹線（東京~博多）で運転されている「のぞみ号」は何両編成か</t>
+    <rPh sb="4" eb="6">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>トウカイドウ</t>
+    </rPh>
+    <rPh sb="11" eb="16">
+      <t>サンヨウシンカンセン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハカタ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ウンテン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ゴウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ナンリョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヘンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年現在の北九州市の人口は約何万人か</t>
+    <rPh sb="4" eb="7">
+      <t>ネンゲンザイ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>キタキュウシュウシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジンコウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ナンマンニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇宙で一番軽い元素は何か</t>
+    <rPh sb="0" eb="2">
+      <t>ウチュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カル</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンソ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘリウム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オゾン</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -372,7 +1335,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -386,6 +1349,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -722,13 +1688,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08DDBE8-B4F7-40DF-B7BA-F006B53A7009}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="2"/>
+    <col min="8" max="8" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -753,7 +1719,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -761,16 +1727,242 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" t="s">
+        <v>98</v>
+      </c>
       <c r="G2" s="1"/>
+      <c r="H2" s="5" t="str">
+        <f>D2</f>
+        <v>ムーンウォーク</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <f>F3</f>
+        <v>二酸化炭素</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" t="s">
+        <v>108</v>
+      </c>
       <c r="G4" s="1"/>
+      <c r="H4" s="5" t="str">
+        <f>C4</f>
+        <v>那覇市</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="5" t="str">
+        <f>C5</f>
+        <v>アイドル</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="5" t="str">
+        <f>D6</f>
+        <v>（上底＋下底）×高さ÷2</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" t="s">
+        <v>123</v>
+      </c>
       <c r="G7" s="1"/>
+      <c r="H7" s="5" t="str">
+        <f>F7</f>
+        <v>ヒンメル</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" t="s">
+        <v>131</v>
+      </c>
       <c r="G9" s="1"/>
+      <c r="H9" s="5" t="str">
+        <f>F9</f>
+        <v>酸化</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="5" t="str">
+        <f>F12</f>
+        <v>水素</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -925,12 +2117,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690150B6-791B-41CB-87CD-167041B46E25}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="2"/>
+    <col min="8" max="8" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -955,7 +2147,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -964,98 +2156,455 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="str">
-        <f>F2</f>
-        <v>店の扉が開いた</v>
+        <v>32</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <f>E2</f>
+        <v>歯科医</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="str">
+        <v>17</v>
+      </c>
+      <c r="H3" s="5" t="str">
         <f>F3</f>
         <v>膝が曲がっていて伸ばすと長い</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="str">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5" t="str">
         <f>F4</f>
         <v>ガスト</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2" t="str">
+        <v>27</v>
+      </c>
+      <c r="H5" s="5" t="str">
         <f>C5</f>
         <v>デンマーク</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="5" t="str">
+        <f>E6</f>
+        <v>ドンコ</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="5" t="str">
+        <f>F7</f>
+        <v>クラッシュロワイヤル</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="5" t="str">
+        <f>C8</f>
+        <v>北島三郎</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="5" t="str">
+        <f>F9</f>
+        <v>キャベツ</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="5" t="str">
+        <f>F10</f>
+        <v>マヒャドデス</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="5" t="str">
+        <f>C11</f>
+        <v>志遠</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="5" t="str">
+        <f>F12</f>
+        <v>うるさい</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>21</v>
+      </c>
+      <c r="D13">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>24</v>
+      </c>
+      <c r="H13" s="5">
+        <f>D13</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="5" t="str">
+        <f>F14</f>
+        <v>ジャパンカップ</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>50</v>
+      </c>
+      <c r="D15">
+        <v>60</v>
+      </c>
+      <c r="E15">
+        <v>90</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="H15" s="5">
+        <f>E15</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="5" t="str">
+        <f>F16</f>
+        <v>羊のスープ</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="5" t="str">
+        <f>E17</f>
+        <v>過学習</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="5" t="str">
+        <f>F18</f>
+        <v>ベリー</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
+      <c r="D19">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>24</v>
+      </c>
+      <c r="F19">
+        <v>22</v>
+      </c>
+      <c r="H19" s="5">
+        <f>F19</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="5" t="str">
+        <f>F20</f>
+        <v>長崎県</v>
       </c>
     </row>
   </sheetData>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F230C4-41A9-46C3-ABA6-25E87BCE0F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765A6FC0-6079-45A9-9782-F1EAD52DAC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="198">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -1265,6 +1265,624 @@
   </si>
   <si>
     <t>オゾン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専は1限何分か</t>
+    <rPh sb="0" eb="5">
+      <t>キタキュウシュウコウセン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナンフン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の効果のうち、菊の花がデザインされているのはどれか</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>キク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1円玉</t>
+    <rPh sb="1" eb="2">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5円玉</t>
+    <rPh sb="1" eb="3">
+      <t>エンダマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10円玉</t>
+    <rPh sb="2" eb="4">
+      <t>エンダマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50円玉</t>
+    <rPh sb="2" eb="4">
+      <t>エンダマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パンダのしっぽの色は一般的に何色か</t>
+    <rPh sb="8" eb="9">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ナニイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒色</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灰色</t>
+    <rPh sb="0" eb="2">
+      <t>ハイイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白色</t>
+    <rPh sb="0" eb="2">
+      <t>シロイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>茶色</t>
+    <rPh sb="0" eb="2">
+      <t>チャイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専の所在地は何区か</t>
+    <rPh sb="0" eb="5">
+      <t>キタキュウシュウコウセン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ショザイチ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナニク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小倉南区</t>
+    <rPh sb="0" eb="4">
+      <t>コクラミナミク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小創南区</t>
+    <rPh sb="0" eb="1">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>キズ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミナミ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小倉商区</t>
+    <rPh sb="0" eb="2">
+      <t>コクラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小倉楠区</t>
+    <rPh sb="0" eb="2">
+      <t>コクラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>クスノキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一番軽い気体は何か</t>
+    <rPh sb="0" eb="2">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カル</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイの首都バンコクの正式名称が長い理由は？</t>
+    <rPh sb="3" eb="5">
+      <t>シュト</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>セイシキメイショウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>リユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歴代の王の名前を繋げたから</t>
+    <rPh sb="0" eb="2">
+      <t>レキダイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神話の神の名前を繋げたから</t>
+    <rPh sb="0" eb="2">
+      <t>シンワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪魔を払うための呪文だから</t>
+    <rPh sb="0" eb="2">
+      <t>アクマ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハラ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジュモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詩がそのまま首都の名前になったから</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年現在の北九州市長の名前は？</t>
+    <rPh sb="4" eb="7">
+      <t>ネンゲンザイ</t>
+    </rPh>
+    <rPh sb="8" eb="13">
+      <t>キタキュウシュウシチョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竹内和久</t>
+    <rPh sb="0" eb="2">
+      <t>タケウチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カズヒサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竹ノ内豊</t>
+    <rPh sb="0" eb="1">
+      <t>タケ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ユタカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竹原ピストル</t>
+    <rPh sb="0" eb="2">
+      <t>タケハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武田信玄</t>
+    <rPh sb="0" eb="4">
+      <t>タケダシンゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュロスの断面が星形の理由は？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見た目をかわいくしてバズらせるため</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シナモンパウダーを多く付着させるため</t>
+    <rPh sb="9" eb="10">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フチャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械のコストを抑えるため</t>
+    <rPh sb="0" eb="2">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>揚げるときに爆発するのを防ぐため</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年11月にディズニーシーでリニューアルするアトラクションの名前にもなっているハリソン・フォードが演じる型破りな冒険家を描いたディズニー作品の名前は？</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カタヤブ</t>
+    </rPh>
+    <rPh sb="59" eb="62">
+      <t>ボウケンカ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>エガ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アバター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターウォーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インディジョーンズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイタニック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一般的な高専とは正式に何と呼ばれる学校制度か</t>
+    <rPh sb="0" eb="3">
+      <t>イッパンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウセン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイシキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高等専門教育学校</t>
+    <rPh sb="0" eb="8">
+      <t>コウトウセンモンキョウイクガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高等専門学校</t>
+    <rPh sb="0" eb="6">
+      <t>コウトウセンモンガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高等専門職学校</t>
+    <rPh sb="0" eb="5">
+      <t>コウトウセンモンショク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高等技術専門学校</t>
+    <rPh sb="0" eb="8">
+      <t>コウトウギジュツセンモンガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年現在マックドナルドのセットで500円のセットはどれか</t>
+    <rPh sb="4" eb="7">
+      <t>ネンゲンザイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>エン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビッグマックセット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マックチキンセット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チーズバーガーセット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>侍マックセット</t>
+    <rPh sb="0" eb="1">
+      <t>サムライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高専本科を卒業すると、原則として得られる称号はどれか</t>
+    <rPh sb="0" eb="2">
+      <t>コウセン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホンカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ショウゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終止</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>準学士</t>
+    <rPh sb="0" eb="3">
+      <t>ジュンガクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学士</t>
+    <rPh sb="0" eb="2">
+      <t>ガクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>博士</t>
+    <rPh sb="0" eb="2">
+      <t>ハカセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>甲子園球場はどこの都道府県にあるか</t>
+    <rPh sb="0" eb="5">
+      <t>コウシエンキュウジョウ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>トドウフケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひょうご</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひらがな</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10円玉と50円玉大きいのはどちらか</t>
+    <rPh sb="2" eb="4">
+      <t>エンダマ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エンダマ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白と黒のシマウマの毛を全て沿ったときの肌は何色か</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ソ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ハダ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナニイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>くろ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専が開講したのは何年か</t>
+    <rPh sb="0" eb="5">
+      <t>キタキュウシュウコウセン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイコウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナンネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平仮名</t>
+    <rPh sb="0" eb="3">
+      <t>ヒラガナ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1335,14 +1953,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1688,13 +2303,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08DDBE8-B4F7-40DF-B7BA-F006B53A7009}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -1719,7 +2333,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -1746,7 +2360,7 @@
         <v>98</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="5" t="str">
+      <c r="H2" t="str">
         <f>D2</f>
         <v>ムーンウォーク</v>
       </c>
@@ -1770,7 +2384,7 @@
       <c r="F3" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="5" t="str">
+      <c r="H3" t="str">
         <f>F3</f>
         <v>二酸化炭素</v>
       </c>
@@ -1795,7 +2409,7 @@
         <v>108</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="5" t="str">
+      <c r="H4" t="str">
         <f>C4</f>
         <v>那覇市</v>
       </c>
@@ -1819,7 +2433,7 @@
       <c r="F5" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="5" t="str">
+      <c r="H5" t="str">
         <f>C5</f>
         <v>アイドル</v>
       </c>
@@ -1843,7 +2457,7 @@
       <c r="F6" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="5" t="str">
+      <c r="H6" t="str">
         <f>D6</f>
         <v>（上底＋下底）×高さ÷2</v>
       </c>
@@ -1868,7 +2482,7 @@
         <v>123</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="5" t="str">
+      <c r="H7" t="str">
         <f>F7</f>
         <v>ヒンメル</v>
       </c>
@@ -1883,7 +2497,7 @@
       <c r="G8" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>1</v>
       </c>
     </row>
@@ -1907,7 +2521,7 @@
         <v>131</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="5" t="str">
+      <c r="H9" t="str">
         <f>F9</f>
         <v>酸化</v>
       </c>
@@ -1922,7 +2536,7 @@
       <c r="G10" t="s">
         <v>126</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10">
         <v>90</v>
       </c>
     </row>
@@ -1936,7 +2550,7 @@
       <c r="G11" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <v>16</v>
       </c>
     </row>
@@ -1959,9 +2573,177 @@
       <c r="F12" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="5" t="str">
+      <c r="H12" t="str">
         <f>F12</f>
         <v>水素</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>50</v>
+      </c>
+      <c r="D13">
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <v>90</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <f>E13</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14" t="str">
+        <f>F14</f>
+        <v>50円玉</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" t="str">
+        <f>E15</f>
+        <v>白色</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" t="s">
+        <v>153</v>
+      </c>
+      <c r="H16" t="str">
+        <f>C16</f>
+        <v>小倉南区</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="str">
+        <f>F17</f>
+        <v>水素</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" t="str">
+        <f>F18</f>
+        <v>詩がそのまま首都の名前になったから</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" t="s">
+        <v>164</v>
+      </c>
+      <c r="H19" t="str">
+        <f>C19</f>
+        <v>竹内和久</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +2760,7 @@
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="2"/>
+    <col min="8" max="8" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2003,11 +2785,35 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f>D2</f>
+        <v>高等専門学校</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2021,13 +2827,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59A4517-58B4-4760-A652-FC3F94417898}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="2"/>
+    <col min="8" max="8" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2052,15 +2858,89 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f>D2</f>
+        <v>マックチキンセット</v>
+      </c>
+    </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" t="s">
+        <v>189</v>
+      </c>
       <c r="G3" s="1"/>
+      <c r="H3" s="4" t="str">
+        <f>D3</f>
+        <v>準学士</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2071,13 +2951,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0197F2A-678A-4724-AC22-85DE23B84306}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="2"/>
+    <col min="8" max="8" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2102,11 +2982,87 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f>F2</f>
+        <v>揚げるときに爆発するのを防ぐため</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H3" s="4" t="str">
+        <f>E3</f>
+        <v>インディジョーンズ</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1965</v>
       </c>
     </row>
   </sheetData>
@@ -2122,7 +3078,6 @@
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2147,7 +3102,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -2155,7 +3110,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
@@ -2173,13 +3128,13 @@
       <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="5" t="str">
+      <c r="H2" t="str">
         <f>E2</f>
         <v>歯科医</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
@@ -2197,13 +3152,13 @@
       <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="5" t="str">
+      <c r="H3" t="str">
         <f>F3</f>
         <v>膝が曲がっていて伸ばすと長い</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B4" t="s">
@@ -2221,7 +3176,7 @@
       <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="5" t="str">
+      <c r="H4" t="str">
         <f>F4</f>
         <v>ガスト</v>
       </c>
@@ -2245,7 +3200,7 @@
       <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="5" t="str">
+      <c r="H5" t="str">
         <f>C5</f>
         <v>デンマーク</v>
       </c>
@@ -2266,7 +3221,7 @@
       <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="5" t="str">
+      <c r="H6" t="str">
         <f>E6</f>
         <v>ドンコ</v>
       </c>
@@ -2290,7 +3245,7 @@
       <c r="F7" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="5" t="str">
+      <c r="H7" t="str">
         <f>F7</f>
         <v>クラッシュロワイヤル</v>
       </c>
@@ -2314,7 +3269,7 @@
       <c r="F8" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="5" t="str">
+      <c r="H8" t="str">
         <f>C8</f>
         <v>北島三郎</v>
       </c>
@@ -2338,7 +3293,7 @@
       <c r="F9" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="5" t="str">
+      <c r="H9" t="str">
         <f>F9</f>
         <v>キャベツ</v>
       </c>
@@ -2362,7 +3317,7 @@
       <c r="F10" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="5" t="str">
+      <c r="H10" t="str">
         <f>F10</f>
         <v>マヒャドデス</v>
       </c>
@@ -2386,7 +3341,7 @@
       <c r="F11" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="5" t="str">
+      <c r="H11" t="str">
         <f>C11</f>
         <v>志遠</v>
       </c>
@@ -2410,7 +3365,7 @@
       <c r="F12" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="5" t="str">
+      <c r="H12" t="str">
         <f>F12</f>
         <v>うるさい</v>
       </c>
@@ -2434,7 +3389,7 @@
       <c r="F13">
         <v>24</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13">
         <f>D13</f>
         <v>22</v>
       </c>
@@ -2458,7 +3413,7 @@
       <c r="F14" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="5" t="str">
+      <c r="H14" t="str">
         <f>F14</f>
         <v>ジャパンカップ</v>
       </c>
@@ -2482,7 +3437,7 @@
       <c r="F15">
         <v>100</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15">
         <f>E15</f>
         <v>90</v>
       </c>
@@ -2506,7 +3461,7 @@
       <c r="F16" t="s">
         <v>77</v>
       </c>
-      <c r="H16" s="5" t="str">
+      <c r="H16" t="str">
         <f>F16</f>
         <v>羊のスープ</v>
       </c>
@@ -2530,7 +3485,7 @@
       <c r="F17" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="5" t="str">
+      <c r="H17" t="str">
         <f>E17</f>
         <v>過学習</v>
       </c>
@@ -2554,7 +3509,7 @@
       <c r="F18" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="5" t="str">
+      <c r="H18" t="str">
         <f>F18</f>
         <v>ベリー</v>
       </c>
@@ -2578,7 +3533,7 @@
       <c r="F19">
         <v>22</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19">
         <f>F19</f>
         <v>22</v>
       </c>
@@ -2602,7 +3557,7 @@
       <c r="F20" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="5" t="str">
+      <c r="H20" t="str">
         <f>F20</f>
         <v>長崎県</v>
       </c>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765A6FC0-6079-45A9-9782-F1EAD52DAC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875290D5-81E6-4373-AB69-022611388EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="2" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="249">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -1883,6 +1883,426 @@
     <rPh sb="0" eb="3">
       <t>ヒラガナ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドンジロウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>これらのアニメの中で仲間外れはどれか</t>
+    <rPh sb="8" eb="9">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ナカマハズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗殺教室</t>
+    <rPh sb="0" eb="4">
+      <t>アンサツキョウシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>逃げ上手の若君</t>
+    <rPh sb="0" eb="1">
+      <t>ニ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウズ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ワカギミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔人探偵脳噛ネウロ</t>
+    <rPh sb="0" eb="4">
+      <t>マジンタンテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ノウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブラッククローバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハロウィンの飾りに必要な「かぼちゃ」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>南瓜</t>
+    <rPh sb="0" eb="2">
+      <t>ミナミウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>西瓜</t>
+    <rPh sb="0" eb="2">
+      <t>ニシウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東瓜</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガシウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北瓜</t>
+    <rPh sb="0" eb="2">
+      <t>キタウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>元祖ハロウィンでジャックオーランタンに使われていた伝統的な野菜はどれか</t>
+    <rPh sb="0" eb="2">
+      <t>ガンソ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>デントウテキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヤサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャガイモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テンサイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スイカ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>富士山の標高は約何メートルか</t>
+    <rPh sb="0" eb="3">
+      <t>フジサン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウコウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トリックオアトリートのフレーズがアメリカハロウィン文化として定着した大まかな時期はいつか</t>
+    <rPh sb="25" eb="27">
+      <t>ブンカ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テイチャク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chioce</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1980年代</t>
+    <rPh sb="4" eb="6">
+      <t>ネンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19世紀半ば</t>
+    <rPh sb="2" eb="4">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17世紀</t>
+    <rPh sb="2" eb="4">
+      <t>セイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1930年代</t>
+    <rPh sb="4" eb="6">
+      <t>ネンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2025年大阪万博のマスコットキャラ「ミャクミャク」のモチーフは何か</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>オオサカバンパク</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポンデリング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いくら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>花冠</t>
+    <rPh sb="0" eb="2">
+      <t>ハナカンムリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>細胞</t>
+    <rPh sb="0" eb="2">
+      <t>サイボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハロウィンとは日本でどの行事にあたる？</t>
+    <rPh sb="7" eb="9">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ギョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>豆まき</t>
+    <rPh sb="0" eb="1">
+      <t>マメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なまはげ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夏祭り</t>
+    <rPh sb="0" eb="2">
+      <t>ナツマツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お盆</t>
+    <rPh sb="1" eb="2">
+      <t>ボン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専は創立何周年か</t>
+    <rPh sb="0" eb="5">
+      <t>キタキュウシュウコウセン</t>
+    </rPh>
+    <rPh sb="6" eb="11">
+      <t>ソウリツナンシュウネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州市の人口最多の区は何区か</t>
+    <rPh sb="0" eb="4">
+      <t>キタキュウシュウシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジンコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サイタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やはたにし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州市の人口最多の区は八幡西区ですが、第2位の区はどこですか</t>
+    <rPh sb="0" eb="4">
+      <t>キタキュウシュウシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジンコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サイタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ヤハタニシ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こくらみなみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「AKIRA」や「がっこうぐらし」がこれにあたる破滅物と呼ばれるSFのサブジャンルを何というか</t>
+    <rPh sb="24" eb="27">
+      <t>ハメツモノ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>片仮名</t>
+    <rPh sb="0" eb="3">
+      <t>カタカナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポストアポカリプス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一番最初に設立された工業高等専門学校はどこか</t>
+    <rPh sb="0" eb="4">
+      <t>イチバンサイショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セツリツ</t>
+    </rPh>
+    <rPh sb="10" eb="18">
+      <t>コウギョウコウトウセンモンガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専</t>
+    <rPh sb="0" eb="5">
+      <t>キタキュウシュウコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>沖縄高専</t>
+    <rPh sb="0" eb="4">
+      <t>オキナワコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>熊本高専</t>
+    <rPh sb="0" eb="4">
+      <t>クマモトコウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明石高専</t>
+    <rPh sb="0" eb="2">
+      <t>アカシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーストラリアのインディーゲームスタジオ「TeamCherry」作のアクションゲームシリーズの名前は？</t>
+    <rPh sb="32" eb="33">
+      <t>サク</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スーパーマリオシリーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイナルファンタジーシリーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星野カービィーシリーズ</t>
+    <rPh sb="0" eb="2">
+      <t>ホシノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メトロシリーズ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1953,7 +2373,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1964,9 +2384,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2303,7 +2720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08DDBE8-B4F7-40DF-B7BA-F006B53A7009}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
@@ -2498,7 +2915,7 @@
         <v>126</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2744,6 +3161,11 @@
       <c r="H19" t="str">
         <f>C19</f>
         <v>竹内和久</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2760,7 +3182,6 @@
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2785,7 +3206,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -2811,9 +3232,81 @@
       <c r="F2" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="4" t="str">
+      <c r="H2" t="str">
         <f>D2</f>
         <v>高等専門学校</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" t="str">
+        <f>C3</f>
+        <v>南瓜</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4" t="str">
+        <f>C4</f>
+        <v>カブ</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H5" t="str">
+        <f>F5</f>
+        <v>お盆</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2827,13 +3320,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59A4517-58B4-4760-A652-FC3F94417898}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2858,7 +3350,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -2884,7 +3376,7 @@
       <c r="F2" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="4" t="str">
+      <c r="H2" t="str">
         <f>D2</f>
         <v>マックチキンセット</v>
       </c>
@@ -2909,7 +3401,7 @@
         <v>189</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="4" t="str">
+      <c r="H3" t="str">
         <f>D3</f>
         <v>準学士</v>
       </c>
@@ -2924,7 +3416,7 @@
       <c r="G4" t="s">
         <v>192</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2938,8 +3430,184 @@
       <c r="G5" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H6" t="str">
+        <f>F6</f>
+        <v>ブラッククローバー</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H7">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D8" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" t="s">
+        <v>220</v>
+      </c>
+      <c r="H8" t="str">
+        <f>F8</f>
+        <v>1930年代</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>221</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H9" t="str">
+        <f>F9</f>
+        <v>細胞</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>244</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F13" t="s">
+        <v>248</v>
+      </c>
+      <c r="H13" t="str">
+        <f>F13</f>
+        <v>メトロシリーズ</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F14" t="s">
+        <v>243</v>
+      </c>
+      <c r="H14" t="str">
+        <f>F14</f>
+        <v>明石高専</v>
       </c>
     </row>
   </sheetData>
@@ -2951,13 +3619,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0197F2A-678A-4724-AC22-85DE23B84306}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
     <col min="3" max="6" width="20.58203125" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -2982,7 +3649,7 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -3008,7 +3675,7 @@
       <c r="F2" t="s">
         <v>169</v>
       </c>
-      <c r="H2" s="4" t="str">
+      <c r="H2" t="str">
         <f>F2</f>
         <v>揚げるときに爆発するのを防ぐため</v>
       </c>
@@ -3032,7 +3699,7 @@
       <c r="F3" t="s">
         <v>174</v>
       </c>
-      <c r="H3" s="4" t="str">
+      <c r="H3" t="str">
         <f>E3</f>
         <v>インディジョーンズ</v>
       </c>
@@ -3047,7 +3714,7 @@
       <c r="G4" t="s">
         <v>197</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3061,8 +3728,22 @@
       <c r="G5" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>1965</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H6" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3221,6 +3902,9 @@
       <c r="E6" t="s">
         <v>35</v>
       </c>
+      <c r="F6" t="s">
+        <v>198</v>
+      </c>
       <c r="H6" t="str">
         <f>E6</f>
         <v>ドンコ</v>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875290D5-81E6-4373-AB69-022611388EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="2" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10900" firstSheet="2" activeTab="4" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875290D5-81E6-4373-AB69-022611388EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0FFFCF8-050A-41B7-BE1E-7CB7561D9D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="10900" firstSheet="2" activeTab="4" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="20" yWindow="1100" windowWidth="19180" windowHeight="10900" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="difficult" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="414">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2303,6 +2304,1785 @@
   </si>
   <si>
     <t>メトロシリーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GooglePixelのCMで最初に出演した芸能人は誰でしょう</t>
+    <rPh sb="15" eb="17">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュツエン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ゲイノウジン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ダレ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小松奈々</t>
+    <rPh sb="0" eb="4">
+      <t>コマツナナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フワちゃん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイナ・ジ・エンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小田凱人</t>
+    <rPh sb="0" eb="2">
+      <t>オダ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通称福岡ドームの福岡市百道にあるソフトバンクの居地のドームの2026年現在の正式名称は？</t>
+    <rPh sb="0" eb="2">
+      <t>ツウショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フクオカ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>フクオカシ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モモチ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キョチ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ネンゲンザイ</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>セイシキメイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>みずほぺいぺいドーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パンダの目の周りが黒いのはなぜか</t>
+    <rPh sb="4" eb="5">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>クロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サングラスの代わりになってるから</t>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目に虫が帰るのを防ぐから</t>
+    <rPh sb="0" eb="1">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ムシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵と戦うときに目を大きく見せる</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タタカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜行性で暗いところでも目がよく見えるようにするため</t>
+    <rPh sb="0" eb="3">
+      <t>ヤコウセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>クラ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JISの生成器名称を答えよ</t>
+    <rPh sb="4" eb="9">
+      <t>セイセイキメイショウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>にほんさんぎょうきかく</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>像の体温調整法は？</t>
+    <rPh sb="0" eb="1">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="2" eb="7">
+      <t>タイオンチョウセイホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耳で仰ぐことで体温調節している。</t>
+    <rPh sb="0" eb="1">
+      <t>ミミ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>タイオンチョウセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鼻息で涼んでいる。</t>
+    <rPh sb="0" eb="2">
+      <t>ハナイキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>スズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>牙が熱を放出する</t>
+    <rPh sb="0" eb="1">
+      <t>キバ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ネツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホウシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そもそも体温が上がらない</t>
+    <rPh sb="4" eb="6">
+      <t>タイオン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年に実施されたセブンイレブンと「ちいかわ」のコラボ商品で実際にない物はどれ？</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>島二郎の味噌汁</t>
+    <rPh sb="0" eb="1">
+      <t>シマ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ジロウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ミソシル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>じゃがバター＆味噌汁</t>
+    <rPh sb="7" eb="10">
+      <t>ミソシル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>島フルーツのパフェ</t>
+    <rPh sb="0" eb="1">
+      <t>シマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>赤魚の煮つけ</t>
+    <rPh sb="0" eb="2">
+      <t>アカザカナ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mrs.green.appleの楽曲でないものを選べ</t>
+    <rPh sb="16" eb="18">
+      <t>ガッキョク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インフェルノ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青と夏</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灰色と青</t>
+    <rPh sb="0" eb="2">
+      <t>ハイイロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライラック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カプコン製のゲームでないものを選ぶ</t>
+    <rPh sb="4" eb="5">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バイオハザード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストリートファイター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターハンター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイレントヒル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新海誠の映画として正しい物を選べ</t>
+    <rPh sb="0" eb="3">
+      <t>シンカイマコト</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>エイガ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サマーウォーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雲の向こう、約束の場所</t>
+    <rPh sb="0" eb="1">
+      <t>クモ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヤクソク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>果てしなきスカーレット</t>
+    <rPh sb="0" eb="1">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未来のミライ</t>
+    <rPh sb="0" eb="2">
+      <t>ミライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウォンバットの生体で間違っている物を選べ</t>
+    <rPh sb="7" eb="9">
+      <t>セイタイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>群れを成す</t>
+    <rPh sb="0" eb="1">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>お尻が固い</t>
+    <rPh sb="1" eb="2">
+      <t>シリ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>糞が四角い</t>
+    <rPh sb="0" eb="1">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>泳ぎが得意</t>
+    <rPh sb="0" eb="1">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トクイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nintendoの代表キャラとして赤い服を着て、ひげを生やした配管工をマリオと言いますが、それのライバルキャラとして登場するメイドインシリーズなどの主人公である黄色い服を着て、Wと書かれた帽子をかぶっているキャラクターの名前を何というか</t>
+    <rPh sb="9" eb="11">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>ハイカンコウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>シュジンコウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>キイロ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ボウシ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワリオ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重音テト</t>
+    <rPh sb="0" eb="2">
+      <t>カサネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホワイトボード下真ん中に書かれている赤い髪のボカロキャラクターの名前は？</t>
+    <rPh sb="7" eb="8">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カミ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初音ミク</t>
+    <rPh sb="0" eb="2">
+      <t>ハツネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鏡音リン</t>
+    <rPh sb="0" eb="1">
+      <t>カガミ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鏡音レン</t>
+    <rPh sb="0" eb="1">
+      <t>カガミ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2008年に初音ミクの歌うボカロとして作成されたが後にドラマがヒットし合唱曲として人気になった曲と言えば何でしょう</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サクラノアメ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高専がない国を選ぶ</t>
+    <rPh sb="0" eb="2">
+      <t>コウセン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カザフスタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンゴル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カンボジア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トルクメニスタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nintendoのゲームとして不適切なものを選べ</t>
+    <rPh sb="15" eb="18">
+      <t>フテキセツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メタルギアソリッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mother</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fire Emblem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メトロイド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ONEPICEで王下七武海に名を連ねていたのは誰？</t>
+    <rPh sb="8" eb="13">
+      <t>オウカシチブカイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツラ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ダレ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トラファルガー・ロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユースタス・キッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジュエリー・ボニー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンキー・D・ルフィ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MPBは日本プロ野球協会の略ですが、メジャーリーグを表す3文字の略語は何？</t>
+    <rPh sb="4" eb="6">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ヤキュウキョウカイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>リャク</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>リャクゴ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MLB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sheep</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大文字</t>
+    <rPh sb="0" eb="3">
+      <t>オオモジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小文字</t>
+    <rPh sb="0" eb="3">
+      <t>コモジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>象を飼っていた徳川将軍と言えばだれになるか</t>
+    <rPh sb="0" eb="1">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>トクガワショウグン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徳川綱吉</t>
+    <rPh sb="0" eb="4">
+      <t>トクガワツナヨシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徳川吉宗</t>
+    <rPh sb="0" eb="4">
+      <t>トクガワヨシムネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徳川家斉</t>
+    <rPh sb="0" eb="2">
+      <t>トクガワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イエナリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徳川家茂</t>
+    <rPh sb="0" eb="4">
+      <t>トクガワイエモチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州高専にないコースはどれ？</t>
+    <rPh sb="0" eb="3">
+      <t>キタキュウシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械創造システムコース</t>
+    <rPh sb="0" eb="2">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>知能ロボットコース</t>
+    <rPh sb="0" eb="2">
+      <t>チノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電気電子コース</t>
+    <rPh sb="0" eb="4">
+      <t>デンキデンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マテリアル化学コース</t>
+    <rPh sb="5" eb="7">
+      <t>カガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>狩り暮らしのスパゲティ</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>グ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この世界の片隅に</t>
+    <rPh sb="2" eb="4">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カタスミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタジオジブリ政策のアニメの作品を選べ</t>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火垂るの墓</t>
+    <rPh sb="0" eb="2">
+      <t>ホタ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メリアと魔女の花</t>
+    <rPh sb="4" eb="6">
+      <t>マジョ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1円玉の重さは何gですか？</t>
+    <rPh sb="1" eb="2">
+      <t>エン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小銭でアラブ数字で表記されてない小銭は何円か</t>
+    <rPh sb="0" eb="2">
+      <t>コゼニ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コゼニ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ナンエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主に物理学で張力をTと表記するとテンションの略だが、Sと表記した場合は何の略か</t>
+    <rPh sb="0" eb="1">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ブツリガク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>リャク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>リャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストリング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>常温状態で液体の元素と言えば化学式で何か</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウオンジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンソ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>カガクシキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Br</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ba</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンパンマンの鼻の数はいくつか</t>
+    <rPh sb="7" eb="8">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンリオシリーズのキキ・ララの身長が同じくらいだとすると1人の身長は約何kmか</t>
+    <rPh sb="15" eb="17">
+      <t>シンチョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>リ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シンチョウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ヤク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンリオシリーズのハローキティの体重はりんご3個分ですが、身長はリンゴ何個分か</t>
+    <rPh sb="16" eb="18">
+      <t>タイジュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コブン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シンチョウ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ナンコブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ふんいき</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雰囲気は正式に何と読む？</t>
+    <rPh sb="0" eb="3">
+      <t>フンイキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイシキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全国で一番多いコンビニは何か</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンコク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セブンイレブン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今年の高専祭のスローガンは何か</t>
+    <rPh sb="0" eb="2">
+      <t>コトシ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>コウセンサイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STARGATHER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STARGAZER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ST@RGAZER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STARGATER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>折り紙の折れた最高回数は12回と言われているが、折り紙を折って月に行ける回数は何回か</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガミ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>サイコウカイスウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ガミ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ナンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>羊は英語でsheepですが、羊を複数形にすると何になるか</t>
+    <rPh sb="0" eb="1">
+      <t>ヒツジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エイゴ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒツジ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>フクスウケイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カントリーマーム問題と呼ばれるジョークでは何年頃に容量が負の数になると言われているか</t>
+    <rPh sb="8" eb="10">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナンネン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ゴロ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>服のセーターは何に由来しているか</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ユライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>汗</t>
+    <rPh sb="0" eb="1">
+      <t>アセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>涙</t>
+    <rPh sb="0" eb="1">
+      <t>ナミダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>唾液</t>
+    <rPh sb="0" eb="2">
+      <t>ダエキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鼻水</t>
+    <rPh sb="0" eb="2">
+      <t>ハナミズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合馬の特産品は何か</t>
+    <rPh sb="0" eb="2">
+      <t>オウマ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>トクサンヒン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chhoice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>きのこ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>たけのこ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トマト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本で最も使用されているスマホの機種はiPhoneであるが、世界で最も使用されている機種は何か</t>
+    <rPh sb="0" eb="2">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キシュ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>キシュ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ナニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ANDROID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホワイトデー発祥の地は何県？</t>
+    <rPh sb="6" eb="8">
+      <t>ハッショウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ナニケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福岡県</t>
+    <rPh sb="0" eb="3">
+      <t>フクオカケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福井県</t>
+    <rPh sb="0" eb="3">
+      <t>フクイケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>福島県</t>
+    <rPh sb="0" eb="3">
+      <t>フクシマケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>群馬県</t>
+    <rPh sb="0" eb="3">
+      <t>グンマケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>江戸時代に出島でオランダ、中国、日本の食文化が融合したことで生まれた料理は何料理と呼ばれるか</t>
+    <rPh sb="0" eb="4">
+      <t>エドジダイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>デジマ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チュウゴク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ショクブンカ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ユウゴウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>リョウリ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>ナニリョウリ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蘭中和料理</t>
+    <rPh sb="0" eb="1">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>和華蘭料理</t>
+    <rPh sb="0" eb="1">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中蘭和料理</t>
+    <rPh sb="0" eb="1">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>華蘭和料理</t>
+    <rPh sb="0" eb="1">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マックドナルド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バーガーキング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モスバーガー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ケンタッキーフライドチキン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>海外で生まれたファストフード店は選ばないでください。</t>
+    <rPh sb="0" eb="2">
+      <t>カイガイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本で唯一単位として扱われる人物は湯川秀樹ですが、1Yukawaと表すと10のマイナス何乗mで表せるか</t>
+    <rPh sb="0" eb="2">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ユイイツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アツカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジンブツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ユカワ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒデキ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ナンジョウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネットスラングで「～な気がする」という言葉を意味し、18族の元素の総称の事である言葉は何でしょうか</t>
+    <rPh sb="11" eb="12">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ゾク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ゲンソ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ソウショウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>きがす</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の中で、ポケモンのタイプ組み合わせに物をある物を選ばないでください。</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎と水</t>
+    <rPh sb="0" eb="1">
+      <t>ホノオ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドラゴンとフェアリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛行と地面</t>
+    <rPh sb="0" eb="2">
+      <t>ヒコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>虫とドラゴン</t>
+    <rPh sb="0" eb="1">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北九州市の特徴として正しい物ではないものを選ばないでください。</t>
+    <rPh sb="0" eb="4">
+      <t>キタキュウシュウシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境都市をうたっている</t>
+    <rPh sb="0" eb="4">
+      <t>カンキョウトシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自転車に乗ってても自転車を奪われる</t>
+    <rPh sb="0" eb="3">
+      <t>ジテンシャ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ジテンシャ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本最大の兵器工場があった</t>
+    <rPh sb="0" eb="4">
+      <t>ニホンサイダイ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ヘイキコウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現在スペースワールドが存在する</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>台湾砂糖産業の父である新渡戸稲造が教育理念としていたものはどれ？</t>
+    <rPh sb="0" eb="2">
+      <t>タイワン</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>サトウサンギョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>チチ</t>
+    </rPh>
+    <rPh sb="11" eb="16">
+      <t>ニトベイナゾウ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>キョウイクリネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>富国強兵</t>
+    <rPh sb="0" eb="4">
+      <t>フコクキョウヘイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>賢くなって人の上に立つ</t>
+    <rPh sb="0" eb="1">
+      <t>カシコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>脱亜入欧</t>
+    <rPh sb="0" eb="4">
+      <t>ダツアニュウオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人格の完成</t>
+    <rPh sb="0" eb="2">
+      <t>ジンカク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハンムラビ法典の〇には〇を歯には歯を〇に入る1文字は？</t>
+    <rPh sb="5" eb="7">
+      <t>ホウテン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>マルニハイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>め</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>太陽の重力を振りきるまでの速度の事を第3宇宙速度と呼びますが、大体秒速何kmであるか</t>
+    <rPh sb="0" eb="2">
+      <t>タイヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジュウリョク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ウチュウソクド</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ダイタイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ビョウソク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日本語にしたときに一番長い文字数の物を選べ</t>
+    <rPh sb="0" eb="3">
+      <t>ニホンゴ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PET</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DNA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PKO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FTA</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2310,7 +4090,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2350,6 +4130,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2368,12 +4157,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2386,8 +4178,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2720,7 +4516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08DDBE8-B4F7-40DF-B7BA-F006B53A7009}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
@@ -3163,11 +4959,6 @@
         <v>竹内和久</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3176,7 +4967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A2EF6D-5559-4B12-AFD8-325115C33FA1}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
@@ -3309,18 +5100,152 @@
         <v>お盆</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F6" t="s">
+        <v>299</v>
+      </c>
+      <c r="H6" t="str">
+        <f>C6</f>
+        <v>重音テト</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F7" t="s">
+        <v>331</v>
+      </c>
+      <c r="H7" t="str">
+        <f>F7</f>
+        <v>マテリアル化学コース</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <f>D8</f>
+        <v>1</v>
+      </c>
+    </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="G9" s="1"/>
+      <c r="A9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="F10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H10" t="str">
+        <f>E10</f>
+        <v>ST@RGAZER</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" t="s">
+        <v>367</v>
+      </c>
+      <c r="C11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D11" t="s">
+        <v>369</v>
+      </c>
+      <c r="E11" t="s">
+        <v>370</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="str">
+        <f>D11</f>
+        <v>たけのこ</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E10" r:id="rId1" xr:uid="{A31F535F-C10B-4E38-A613-D09125D6436E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59A4517-58B4-4760-A652-FC3F94417898}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
@@ -3610,6 +5535,442 @@
         <v>明石高専</v>
       </c>
     </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>273</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D16" t="s">
+        <v>275</v>
+      </c>
+      <c r="E16" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" t="s">
+        <v>277</v>
+      </c>
+      <c r="H16" t="str">
+        <f>E16</f>
+        <v>灰色と青</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>283</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>284</v>
+      </c>
+      <c r="D17" t="s">
+        <v>285</v>
+      </c>
+      <c r="E17" t="s">
+        <v>286</v>
+      </c>
+      <c r="F17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H17" t="str">
+        <f>D17</f>
+        <v>雲の向こう、約束の場所</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>293</v>
+      </c>
+      <c r="B18" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" t="s">
+        <v>237</v>
+      </c>
+      <c r="H18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B19" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" t="s">
+        <v>237</v>
+      </c>
+      <c r="H19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" t="s">
+        <v>306</v>
+      </c>
+      <c r="H20" t="str">
+        <f>D20</f>
+        <v>モンゴル</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>309</v>
+      </c>
+      <c r="D21" t="s">
+        <v>310</v>
+      </c>
+      <c r="E21" t="s">
+        <v>308</v>
+      </c>
+      <c r="F21" t="s">
+        <v>311</v>
+      </c>
+      <c r="H21" t="str">
+        <f>E21</f>
+        <v>メタルギアソリッド</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>316</v>
+      </c>
+      <c r="D22" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22" t="s">
+        <v>315</v>
+      </c>
+      <c r="H22" t="str">
+        <f>D22</f>
+        <v>トラファルガー・ロー</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" t="s">
+        <v>320</v>
+      </c>
+      <c r="H23" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>359</v>
+      </c>
+      <c r="B24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" t="s">
+        <v>321</v>
+      </c>
+      <c r="H24" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>348</v>
+      </c>
+      <c r="B27" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>351</v>
+      </c>
+      <c r="B28" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" t="s">
+        <v>237</v>
+      </c>
+      <c r="H28" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>358</v>
+      </c>
+      <c r="B29" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>360</v>
+      </c>
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" t="s">
+        <v>126</v>
+      </c>
+      <c r="H30">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>362</v>
+      </c>
+      <c r="D31" t="s">
+        <v>363</v>
+      </c>
+      <c r="E31" t="s">
+        <v>364</v>
+      </c>
+      <c r="F31" t="s">
+        <v>365</v>
+      </c>
+      <c r="H31" t="str">
+        <f>C31</f>
+        <v>汗</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>371</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" t="s">
+        <v>320</v>
+      </c>
+      <c r="H32" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>373</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>374</v>
+      </c>
+      <c r="D33" t="s">
+        <v>375</v>
+      </c>
+      <c r="E33" t="s">
+        <v>376</v>
+      </c>
+      <c r="F33" t="s">
+        <v>377</v>
+      </c>
+      <c r="H33" t="str">
+        <f>F33</f>
+        <v>群馬県</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>387</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>383</v>
+      </c>
+      <c r="D34" t="s">
+        <v>384</v>
+      </c>
+      <c r="E34" t="s">
+        <v>385</v>
+      </c>
+      <c r="F34" t="s">
+        <v>386</v>
+      </c>
+      <c r="H34" t="str">
+        <f>E34</f>
+        <v>モスバーガー</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>389</v>
+      </c>
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="G35" t="s">
+        <v>197</v>
+      </c>
+      <c r="H35" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>401</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>402</v>
+      </c>
+      <c r="D36" t="s">
+        <v>403</v>
+      </c>
+      <c r="E36" t="s">
+        <v>404</v>
+      </c>
+      <c r="F36" t="s">
+        <v>405</v>
+      </c>
+      <c r="H36" t="str">
+        <f>F36</f>
+        <v>人格の完成</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>406</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="G37" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>409</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>410</v>
+      </c>
+      <c r="D38" t="s">
+        <v>411</v>
+      </c>
+      <c r="E38" t="s">
+        <v>412</v>
+      </c>
+      <c r="F38" t="s">
+        <v>413</v>
+      </c>
+      <c r="H38" t="str">
+        <f>C38</f>
+        <v>PET</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3619,7 +5980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0197F2A-678A-4724-AC22-85DE23B84306}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
@@ -3746,6 +6107,275 @@
         <v>238</v>
       </c>
     </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E7" t="s">
+        <v>259</v>
+      </c>
+      <c r="F7" t="s">
+        <v>260</v>
+      </c>
+      <c r="H7" t="str">
+        <f>D7</f>
+        <v>サングラスの代わりになってるから</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H9" t="str">
+        <f>C9</f>
+        <v>耳で仰ぐことで体温調節している。</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" t="s">
+        <v>281</v>
+      </c>
+      <c r="F10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H10" t="str">
+        <f>F10</f>
+        <v>サイレントヒル</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" t="s">
+        <v>290</v>
+      </c>
+      <c r="E11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F11" t="s">
+        <v>292</v>
+      </c>
+      <c r="H11" t="str">
+        <f>C11</f>
+        <v>群れを成す</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" t="s">
+        <v>325</v>
+      </c>
+      <c r="F12" t="s">
+        <v>326</v>
+      </c>
+      <c r="H12" t="str">
+        <f>D12</f>
+        <v>徳川吉宗</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>334</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>333</v>
+      </c>
+      <c r="D13" t="s">
+        <v>335</v>
+      </c>
+      <c r="E13" t="s">
+        <v>336</v>
+      </c>
+      <c r="F13" t="s">
+        <v>332</v>
+      </c>
+      <c r="H13" t="str">
+        <f>D13</f>
+        <v>火垂るの墓</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>339</v>
+      </c>
+      <c r="B14" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>341</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" t="s">
+        <v>343</v>
+      </c>
+      <c r="E15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F15" t="s">
+        <v>345</v>
+      </c>
+      <c r="H15" t="str">
+        <f>C15</f>
+        <v>Br</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>347</v>
+      </c>
+      <c r="B16" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>391</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>392</v>
+      </c>
+      <c r="D17" t="s">
+        <v>393</v>
+      </c>
+      <c r="E17" t="s">
+        <v>394</v>
+      </c>
+      <c r="F17" t="s">
+        <v>395</v>
+      </c>
+      <c r="H17" t="str">
+        <f>F17</f>
+        <v>虫とドラゴン</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>396</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" t="s">
+        <v>398</v>
+      </c>
+      <c r="E18" t="s">
+        <v>399</v>
+      </c>
+      <c r="F18" t="s">
+        <v>400</v>
+      </c>
+      <c r="H18" t="str">
+        <f>C18</f>
+        <v>環境都市をうたっている</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>408</v>
+      </c>
+      <c r="B19" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3754,7 +6384,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690150B6-791B-41CB-87CD-167041B46E25}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="45.58203125" customWidth="1"/>
@@ -4246,6 +6876,92 @@
         <v>長崎県</v>
       </c>
     </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" t="s">
+        <v>252</v>
+      </c>
+      <c r="F21" t="s">
+        <v>253</v>
+      </c>
+      <c r="H21" t="str">
+        <f>C21</f>
+        <v>小松奈々</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>268</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>269</v>
+      </c>
+      <c r="D22" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" t="s">
+        <v>272</v>
+      </c>
+      <c r="H22" t="str">
+        <f>C22</f>
+        <v>島二郎の味噌汁</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>378</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>379</v>
+      </c>
+      <c r="D23" t="s">
+        <v>380</v>
+      </c>
+      <c r="E23" t="s">
+        <v>381</v>
+      </c>
+      <c r="F23" t="s">
+        <v>382</v>
+      </c>
+      <c r="H23" t="str">
+        <f>D23</f>
+        <v>和華蘭料理</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>388</v>
+      </c>
+      <c r="B24" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0FFFCF8-050A-41B7-BE1E-7CB7561D9D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC012CBE-25A9-497B-8E22-F58707185793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="1100" windowWidth="19180" windowHeight="10900" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="difficult" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="415">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -866,13 +865,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>算ウォーク</t>
-    <rPh sb="0" eb="1">
-      <t>サン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>コーラなどの炭酸ジュースで、シュワシュワした刺激をもたらしている気体は何か</t>
     <rPh sb="6" eb="8">
       <t>タンサン</t>
@@ -1779,13 +1771,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>終止</t>
-    <rPh sb="0" eb="2">
-      <t>シュウシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>準学士</t>
     <rPh sb="0" eb="3">
       <t>ジュンガクシ</t>
@@ -2149,28 +2134,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>北九州市の人口最多の区は何区か</t>
-    <rPh sb="0" eb="4">
-      <t>キタキュウシュウシ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジンコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>サイタ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>やはたにし</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2376,10 +2339,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>みずほぺいぺいドーム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>パンダの目の周りが黒いのはなぜか</t>
     <rPh sb="4" eb="5">
       <t>メ</t>
@@ -2876,19 +2835,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>高専がない国を選ぶ</t>
-    <rPh sb="0" eb="2">
-      <t>コウセン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>クニ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>エラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>カザフスタン</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3118,19 +3064,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スタジオジブリ政策のアニメの作品を選べ</t>
-    <rPh sb="7" eb="9">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>サクヒン</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>エラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>火垂るの墓</t>
     <rPh sb="0" eb="2">
       <t>ホタ</t>
@@ -3167,25 +3100,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>小銭でアラブ数字で表記されてない小銭は何円か</t>
-    <rPh sb="0" eb="2">
-      <t>コゼニ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>スウジ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウキ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>コゼニ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ナンエン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>主に物理学で張力をTと表記するとテンションの略だが、Sと表記した場合は何の略か</t>
     <rPh sb="0" eb="1">
       <t>オモ</t>
@@ -3438,34 +3352,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カントリーマーム問題と呼ばれるジョークでは何年頃に容量が負の数になると言われているか</t>
-    <rPh sb="8" eb="10">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ナンネン</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ゴロ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ヨウリョウ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>服のセーターは何に由来しているか</t>
     <rPh sb="0" eb="1">
       <t>フク</t>
@@ -4083,6 +3969,132 @@
   </si>
   <si>
     <t>FTA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高専がある国を選ぶ</t>
+    <rPh sb="0" eb="2">
+      <t>コウセン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタジオジブリ製作のアニメの作品を選べ</t>
+    <rPh sb="7" eb="9">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修士</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カントリーマァム問題と呼ばれるジョークでは何年頃に容量が負の数になると言われているか</t>
+    <rPh sb="8" eb="10">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナンネン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ゴロ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小銭の中でアラブ数字で表記されてない小銭は何円か</t>
+    <rPh sb="0" eb="2">
+      <t>コゼニ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コゼニ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナンエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026年現在北九州市の人口最多の区は何区か</t>
+    <rPh sb="4" eb="7">
+      <t>ネンゲンザイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>キタキュウシュウシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジンコウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サイタ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>みずほペイペイドーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平仮名,片仮名</t>
+    <rPh sb="0" eb="3">
+      <t>ヒラガナ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>カタカナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンウォーク</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4570,7 +4582,7 @@
         <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>414</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" t="str">
@@ -4580,22 +4592,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>99</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>100</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>101</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>102</v>
-      </c>
-      <c r="F3" t="s">
-        <v>103</v>
       </c>
       <c r="H3" t="str">
         <f>F3</f>
@@ -4604,22 +4616,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>104</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>105</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>106</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>107</v>
-      </c>
-      <c r="F4" t="s">
-        <v>108</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" t="str">
@@ -4629,22 +4641,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>109</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>110</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>111</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>112</v>
-      </c>
-      <c r="F5" t="s">
-        <v>113</v>
       </c>
       <c r="H5" t="str">
         <f>C5</f>
@@ -4653,22 +4665,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
         <v>114</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>116</v>
       </c>
-      <c r="D6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>117</v>
-      </c>
-      <c r="F6" t="s">
-        <v>118</v>
       </c>
       <c r="H6" t="str">
         <f>D6</f>
@@ -4677,22 +4689,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>119</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>120</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>121</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>122</v>
-      </c>
-      <c r="F7" t="s">
-        <v>123</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" t="str">
@@ -4702,13 +4714,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
         <v>124</v>
       </c>
-      <c r="B8" t="s">
+      <c r="G8" t="s">
         <v>125</v>
-      </c>
-      <c r="G8" t="s">
-        <v>126</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -4716,38 +4728,38 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>127</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>128</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>129</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>130</v>
-      </c>
-      <c r="F9" t="s">
-        <v>131</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" t="str">
-        <f>F9</f>
-        <v>酸化</v>
+        <f>E9</f>
+        <v>還元</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" t="s">
         <v>125</v>
-      </c>
-      <c r="G10" t="s">
-        <v>126</v>
       </c>
       <c r="H10">
         <v>90</v>
@@ -4755,13 +4767,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" t="s">
         <v>125</v>
-      </c>
-      <c r="G11" t="s">
-        <v>126</v>
       </c>
       <c r="H11">
         <v>16</v>
@@ -4769,22 +4781,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>134</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>135</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>136</v>
       </c>
-      <c r="E12" t="s">
-        <v>137</v>
-      </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H12" t="str">
         <f>F12</f>
@@ -4793,7 +4805,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -4817,22 +4829,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
         <v>139</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>140</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>141</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>142</v>
-      </c>
-      <c r="F14" t="s">
-        <v>143</v>
       </c>
       <c r="H14" t="str">
         <f>F14</f>
@@ -4841,22 +4853,22 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
         <v>144</v>
       </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>145</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>146</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>147</v>
-      </c>
-      <c r="F15" t="s">
-        <v>148</v>
       </c>
       <c r="H15" t="str">
         <f>E15</f>
@@ -4865,22 +4877,22 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
         <v>149</v>
       </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>150</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>151</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>152</v>
-      </c>
-      <c r="F16" t="s">
-        <v>153</v>
       </c>
       <c r="H16" t="str">
         <f>C16</f>
@@ -4889,22 +4901,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H17" t="str">
         <f>F17</f>
@@ -4913,22 +4925,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
         <v>155</v>
       </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>156</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>157</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>158</v>
-      </c>
-      <c r="F18" t="s">
-        <v>159</v>
       </c>
       <c r="H18" t="str">
         <f>F18</f>
@@ -4937,22 +4949,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
         <v>160</v>
       </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>161</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>162</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>163</v>
-      </c>
-      <c r="F19" t="s">
-        <v>164</v>
       </c>
       <c r="H19" t="str">
         <f>C19</f>
@@ -5006,22 +5018,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>175</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>176</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>177</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>178</v>
-      </c>
-      <c r="F2" t="s">
-        <v>179</v>
       </c>
       <c r="H2" t="str">
         <f>D2</f>
@@ -5030,22 +5042,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" t="s">
         <v>204</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>205</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>206</v>
-      </c>
-      <c r="E3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F3" t="s">
-        <v>208</v>
       </c>
       <c r="H3" t="str">
         <f>C3</f>
@@ -5054,22 +5066,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" t="s">
         <v>209</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" t="s">
-        <v>211</v>
-      </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H4" t="str">
         <f>C4</f>
@@ -5078,22 +5090,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" t="s">
         <v>226</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>227</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>228</v>
-      </c>
-      <c r="E5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F5" t="s">
-        <v>230</v>
       </c>
       <c r="H5" t="str">
         <f>F5</f>
@@ -5102,22 +5114,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" t="s">
         <v>295</v>
-      </c>
-      <c r="D6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E6" t="s">
-        <v>298</v>
-      </c>
-      <c r="F6" t="s">
-        <v>299</v>
       </c>
       <c r="H6" t="str">
         <f>C6</f>
@@ -5126,22 +5138,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D7" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E7" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F7" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H7" t="str">
         <f>F7</f>
@@ -5150,7 +5162,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -5174,36 +5186,36 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H9" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D10" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="F10" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="H10" t="str">
         <f>E10</f>
@@ -5212,19 +5224,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B11" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C11" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="D11" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="E11" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
@@ -5284,22 +5296,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>180</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>181</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>182</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>183</v>
-      </c>
-      <c r="F2" t="s">
-        <v>184</v>
       </c>
       <c r="H2" t="str">
         <f>D2</f>
@@ -5308,22 +5320,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D3" t="s">
         <v>185</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>186</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>187</v>
-      </c>
-      <c r="E3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F3" t="s">
-        <v>189</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" t="str">
@@ -5333,27 +5345,27 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" t="s">
         <v>190</v>
       </c>
-      <c r="B4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" t="s">
-        <v>192</v>
-      </c>
       <c r="H4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" t="s">
         <v>125</v>
-      </c>
-      <c r="G5" t="s">
-        <v>126</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -5361,22 +5373,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" t="s">
         <v>199</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>200</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>201</v>
-      </c>
-      <c r="E6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F6" t="s">
-        <v>203</v>
       </c>
       <c r="H6" t="str">
         <f>F6</f>
@@ -5385,13 +5397,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" t="s">
         <v>125</v>
-      </c>
-      <c r="G7" t="s">
-        <v>126</v>
       </c>
       <c r="H7">
         <v>3776</v>
@@ -5399,22 +5411,22 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" t="s">
         <v>215</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>216</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>217</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>218</v>
-      </c>
-      <c r="E8" t="s">
-        <v>219</v>
-      </c>
-      <c r="F8" t="s">
-        <v>220</v>
       </c>
       <c r="H8" t="str">
         <f>F8</f>
@@ -5423,22 +5435,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" t="s">
         <v>221</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>222</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>223</v>
-      </c>
-      <c r="E9" t="s">
-        <v>224</v>
-      </c>
-      <c r="F9" t="s">
-        <v>225</v>
       </c>
       <c r="H9" t="str">
         <f>F9</f>
@@ -5447,13 +5459,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" t="s">
         <v>125</v>
-      </c>
-      <c r="G10" t="s">
-        <v>126</v>
       </c>
       <c r="H10">
         <v>61</v>
@@ -5461,50 +5473,50 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>411</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E13" t="s">
         <v>244</v>
       </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
         <v>245</v>
-      </c>
-      <c r="D13" t="s">
-        <v>246</v>
-      </c>
-      <c r="E13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F13" t="s">
-        <v>248</v>
       </c>
       <c r="H13" t="str">
         <f>F13</f>
@@ -5513,22 +5525,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D14" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" t="s">
         <v>239</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
         <v>240</v>
-      </c>
-      <c r="D14" t="s">
-        <v>241</v>
-      </c>
-      <c r="E14" t="s">
-        <v>242</v>
-      </c>
-      <c r="F14" t="s">
-        <v>243</v>
       </c>
       <c r="H14" t="str">
         <f>F14</f>
@@ -5537,36 +5549,36 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G15" t="s">
-        <v>197</v>
+        <v>413</v>
       </c>
       <c r="H15" t="s">
-        <v>255</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>270</v>
+      </c>
+      <c r="D16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" t="s">
         <v>273</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D16" t="s">
-        <v>275</v>
-      </c>
-      <c r="E16" t="s">
-        <v>276</v>
-      </c>
-      <c r="F16" t="s">
-        <v>277</v>
       </c>
       <c r="H16" t="str">
         <f>E16</f>
@@ -5575,22 +5587,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F17" t="s">
         <v>283</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>284</v>
-      </c>
-      <c r="D17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E17" t="s">
-        <v>286</v>
-      </c>
-      <c r="F17" t="s">
-        <v>287</v>
       </c>
       <c r="H17" t="str">
         <f>D17</f>
@@ -5599,50 +5611,50 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H18" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H19" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D20" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E20" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F20" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H20" t="str">
         <f>D20</f>
@@ -5651,22 +5663,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D21" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E21" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F21" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H21" t="str">
         <f>E21</f>
@@ -5675,22 +5687,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D22" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E22" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F22" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H22" t="str">
         <f>D22</f>
@@ -5699,41 +5711,41 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G23" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H23" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G24" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="H24" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" t="s">
         <v>125</v>
-      </c>
-      <c r="G25" t="s">
-        <v>126</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -5741,13 +5753,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>338</v>
+        <v>410</v>
       </c>
       <c r="B26" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" t="s">
         <v>125</v>
-      </c>
-      <c r="G26" t="s">
-        <v>126</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -5755,13 +5767,13 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -5769,27 +5781,27 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H28" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29" t="s">
         <v>125</v>
-      </c>
-      <c r="G29" t="s">
-        <v>126</v>
       </c>
       <c r="H29">
         <v>42</v>
@@ -5797,13 +5809,13 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="B30" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" t="s">
         <v>125</v>
-      </c>
-      <c r="G30" t="s">
-        <v>126</v>
       </c>
       <c r="H30">
         <v>2040</v>
@@ -5811,22 +5823,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="D31" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E31" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="F31" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H31" t="str">
         <f>C31</f>
@@ -5835,36 +5847,36 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="G32" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="H32" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="D33" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E33" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="F33" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="H33" t="str">
         <f>F33</f>
@@ -5873,22 +5885,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D34" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="E34" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F34" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="H34" t="str">
         <f>E34</f>
@@ -5897,36 +5909,36 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G35" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H35" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B36" t="s">
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D36" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E36" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="F36" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="H36" t="str">
         <f>F36</f>
@@ -5935,36 +5947,36 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H37" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="D38" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="E38" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="F38" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="H38" t="str">
         <f>C38</f>
@@ -6019,22 +6031,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>165</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>166</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>167</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>168</v>
-      </c>
-      <c r="F2" t="s">
-        <v>169</v>
       </c>
       <c r="H2" t="str">
         <f>F2</f>
@@ -6043,22 +6055,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>170</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>171</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>172</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>173</v>
-      </c>
-      <c r="F3" t="s">
-        <v>174</v>
       </c>
       <c r="H3" t="str">
         <f>E3</f>
@@ -6067,27 +6079,27 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" t="s">
         <v>125</v>
-      </c>
-      <c r="G5" t="s">
-        <v>126</v>
       </c>
       <c r="H5">
         <v>1965</v>
@@ -6095,36 +6107,36 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" t="s">
         <v>256</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E7" t="s">
-        <v>259</v>
-      </c>
-      <c r="F7" t="s">
-        <v>260</v>
       </c>
       <c r="H7" t="str">
         <f>D7</f>
@@ -6133,36 +6145,36 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" t="s">
         <v>263</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" t="s">
-        <v>265</v>
-      </c>
-      <c r="E9" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" t="s">
-        <v>267</v>
       </c>
       <c r="H9" t="str">
         <f>C9</f>
@@ -6171,22 +6183,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F10" t="s">
         <v>278</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>279</v>
-      </c>
-      <c r="D10" t="s">
-        <v>280</v>
-      </c>
-      <c r="E10" t="s">
-        <v>281</v>
-      </c>
-      <c r="F10" t="s">
-        <v>282</v>
       </c>
       <c r="H10" t="str">
         <f>F10</f>
@@ -6195,22 +6207,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D11" t="s">
+        <v>286</v>
+      </c>
+      <c r="E11" t="s">
+        <v>287</v>
+      </c>
+      <c r="F11" t="s">
         <v>288</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>289</v>
-      </c>
-      <c r="D11" t="s">
-        <v>290</v>
-      </c>
-      <c r="E11" t="s">
-        <v>291</v>
-      </c>
-      <c r="F11" t="s">
-        <v>292</v>
       </c>
       <c r="H11" t="str">
         <f>C11</f>
@@ -6219,22 +6231,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E12" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H12" t="str">
         <f>D12</f>
@@ -6243,22 +6255,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>407</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D13" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E13" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F13" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="H13" t="str">
         <f>D13</f>
@@ -6267,36 +6279,36 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D15" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="H15" t="str">
         <f>C15</f>
@@ -6305,13 +6317,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" t="s">
         <v>125</v>
-      </c>
-      <c r="G16" t="s">
-        <v>126</v>
       </c>
       <c r="H16">
         <v>1700</v>
@@ -6319,22 +6331,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D17" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="E17" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F17" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H17" t="str">
         <f>F17</f>
@@ -6343,22 +6355,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D18" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E18" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F18" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="H18" t="str">
         <f>C18</f>
@@ -6367,10 +6379,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19">
         <v>42</v>
@@ -6533,7 +6545,7 @@
         <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H6" t="str">
         <f>E6</f>
@@ -6878,22 +6890,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>247</v>
+      </c>
+      <c r="D21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E21" t="s">
         <v>249</v>
       </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="F21" t="s">
         <v>250</v>
-      </c>
-      <c r="D21" t="s">
-        <v>251</v>
-      </c>
-      <c r="E21" t="s">
-        <v>252</v>
-      </c>
-      <c r="F21" t="s">
-        <v>253</v>
       </c>
       <c r="H21" t="str">
         <f>C21</f>
@@ -6902,22 +6914,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D22" t="s">
+        <v>266</v>
+      </c>
+      <c r="E22" t="s">
+        <v>267</v>
+      </c>
+      <c r="F22" t="s">
         <v>268</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>269</v>
-      </c>
-      <c r="D22" t="s">
-        <v>270</v>
-      </c>
-      <c r="E22" t="s">
-        <v>271</v>
-      </c>
-      <c r="F22" t="s">
-        <v>272</v>
       </c>
       <c r="H22" t="str">
         <f>C22</f>
@@ -6926,22 +6938,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="D23" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E23" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="F23" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="H23" t="str">
         <f>D23</f>
@@ -6950,13 +6962,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" t="s">
         <v>125</v>
-      </c>
-      <c r="G24" t="s">
-        <v>126</v>
       </c>
       <c r="H24">
         <v>15</v>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC012CBE-25A9-497B-8E22-F58707185793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93574C4-D48B-4DAE-9FFF-215404D14D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
   <sheets>
     <sheet name="easy" sheetId="1" r:id="rId1"/>
@@ -1823,31 +1823,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>白と黒のシマウマの毛を全て沿ったときの肌は何色か</t>
-    <rPh sb="0" eb="1">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>クロ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ケ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>スベ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ソ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ハダ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ナニイロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>くろ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2410,16 +2385,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>JISの生成器名称を答えよ</t>
-    <rPh sb="4" eb="9">
-      <t>セイセイキメイショウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>にほんさんぎょうきかく</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2653,22 +2618,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ウォンバットの生体で間違っている物を選べ</t>
-    <rPh sb="7" eb="9">
-      <t>セイタイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>モノ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>エラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>群れを成す</t>
     <rPh sb="0" eb="1">
       <t>ム</t>
@@ -2824,13 +2773,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2008年に初音ミクの歌うボカロとして作成されたが後にドラマがヒットし合唱曲として人気になった曲と言えば何でしょう</t>
-    <rPh sb="4" eb="5">
-      <t>ネン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>サクラノアメ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3972,19 +3914,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>高専がある国を選ぶ</t>
-    <rPh sb="0" eb="2">
-      <t>コウセン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>クニ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>エラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スタジオジブリ製作のアニメの作品を選べ</t>
     <rPh sb="7" eb="9">
       <t>セイサク</t>
@@ -4095,6 +4024,80 @@
   </si>
   <si>
     <t>サンウォーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2008年に初音ミクの歌うボカロとして作成されたが後に映画がヒットし合唱曲として人気になった曲と言えば何でしょう</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>エイガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JISの正式名称を答えよ</t>
+    <rPh sb="4" eb="6">
+      <t>セイシキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>メイショウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウォンバットの生態で間違っている物を選べ</t>
+    <rPh sb="7" eb="9">
+      <t>セイタイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白と黒のシマウマの毛を全て剃ったときの肌は何色か</t>
+    <rPh sb="0" eb="1">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ハダ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ナニイロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高専がある国を選んでください。</t>
+    <rPh sb="0" eb="2">
+      <t>コウセン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>クニ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>エラ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4582,7 +4585,7 @@
         <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" t="str">
@@ -5042,22 +5045,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>202</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>203</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>204</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>205</v>
-      </c>
-      <c r="F3" t="s">
-        <v>206</v>
       </c>
       <c r="H3" t="str">
         <f>C3</f>
@@ -5066,22 +5069,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" t="s">
         <v>207</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" t="s">
-        <v>208</v>
       </c>
       <c r="H4" t="str">
         <f>C4</f>
@@ -5090,22 +5093,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>224</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>225</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>226</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>227</v>
-      </c>
-      <c r="F5" t="s">
-        <v>228</v>
       </c>
       <c r="H5" t="str">
         <f>F5</f>
@@ -5114,22 +5117,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" t="s">
         <v>292</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D6" t="s">
-        <v>293</v>
-      </c>
-      <c r="E6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F6" t="s">
-        <v>295</v>
       </c>
       <c r="H6" t="str">
         <f>C6</f>
@@ -5138,22 +5141,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F7" t="s">
         <v>322</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" t="s">
-        <v>324</v>
-      </c>
-      <c r="E7" t="s">
-        <v>325</v>
-      </c>
-      <c r="F7" t="s">
-        <v>326</v>
       </c>
       <c r="H7" t="str">
         <f>F7</f>
@@ -5162,7 +5165,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -5186,36 +5189,36 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B9" t="s">
         <v>124</v>
       </c>
       <c r="G9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H9" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" t="s">
+        <v>344</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F10" t="s">
         <v>346</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>347</v>
-      </c>
-      <c r="D10" t="s">
-        <v>348</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F10" t="s">
-        <v>350</v>
       </c>
       <c r="H10" t="str">
         <f>E10</f>
@@ -5224,19 +5227,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" t="s">
+        <v>357</v>
+      </c>
+      <c r="E11" t="s">
         <v>358</v>
-      </c>
-      <c r="B11" t="s">
-        <v>359</v>
-      </c>
-      <c r="C11" t="s">
-        <v>360</v>
-      </c>
-      <c r="D11" t="s">
-        <v>361</v>
-      </c>
-      <c r="E11" t="s">
-        <v>362</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
@@ -5326,7 +5329,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D3" t="s">
         <v>185</v>
@@ -5373,22 +5376,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>197</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>198</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>199</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>200</v>
-      </c>
-      <c r="F6" t="s">
-        <v>201</v>
       </c>
       <c r="H6" t="str">
         <f>F6</f>
@@ -5397,7 +5400,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B7" t="s">
         <v>124</v>
@@ -5411,22 +5414,22 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" t="s">
         <v>213</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>214</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>215</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>216</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>217</v>
-      </c>
-      <c r="F8" t="s">
-        <v>218</v>
       </c>
       <c r="H8" t="str">
         <f>F8</f>
@@ -5435,22 +5438,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>219</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>220</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>221</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>222</v>
-      </c>
-      <c r="F9" t="s">
-        <v>223</v>
       </c>
       <c r="H9" t="str">
         <f>F9</f>
@@ -5459,7 +5462,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B10" t="s">
         <v>124</v>
@@ -5473,50 +5476,50 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B11" t="s">
         <v>124</v>
       </c>
       <c r="G11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B12" t="s">
         <v>124</v>
       </c>
       <c r="G12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
         <v>241</v>
       </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>242</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>243</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>244</v>
-      </c>
-      <c r="F13" t="s">
-        <v>245</v>
       </c>
       <c r="H13" t="str">
         <f>F13</f>
@@ -5525,22 +5528,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
         <v>236</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>237</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>238</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>239</v>
-      </c>
-      <c r="F14" t="s">
-        <v>240</v>
       </c>
       <c r="H14" t="str">
         <f>F14</f>
@@ -5549,36 +5552,36 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B15" t="s">
         <v>124</v>
       </c>
       <c r="G15" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H15" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>268</v>
+      </c>
+      <c r="D16" t="s">
         <v>269</v>
       </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>270</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>271</v>
-      </c>
-      <c r="E16" t="s">
-        <v>272</v>
-      </c>
-      <c r="F16" t="s">
-        <v>273</v>
       </c>
       <c r="H16" t="str">
         <f>E16</f>
@@ -5587,22 +5590,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>277</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" t="s">
         <v>279</v>
       </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>280</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>281</v>
-      </c>
-      <c r="E17" t="s">
-        <v>282</v>
-      </c>
-      <c r="F17" t="s">
-        <v>283</v>
       </c>
       <c r="H17" t="str">
         <f>D17</f>
@@ -5611,50 +5614,50 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B18" t="s">
         <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H18" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>296</v>
+        <v>410</v>
       </c>
       <c r="B19" t="s">
         <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H19" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D20" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E20" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="H20" t="str">
         <f>D20</f>
@@ -5663,22 +5666,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>300</v>
+      </c>
+      <c r="D21" t="s">
+        <v>301</v>
+      </c>
+      <c r="E21" t="s">
+        <v>299</v>
+      </c>
+      <c r="F21" t="s">
         <v>302</v>
-      </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>304</v>
-      </c>
-      <c r="D21" t="s">
-        <v>305</v>
-      </c>
-      <c r="E21" t="s">
-        <v>303</v>
-      </c>
-      <c r="F21" t="s">
-        <v>306</v>
       </c>
       <c r="H21" t="str">
         <f>E21</f>
@@ -5687,22 +5690,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>303</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
         <v>307</v>
       </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>311</v>
-      </c>
       <c r="D22" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E22" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F22" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H22" t="str">
         <f>D22</f>
@@ -5711,35 +5714,35 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B23" t="s">
         <v>124</v>
       </c>
       <c r="G23" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H23" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B24" t="s">
         <v>124</v>
       </c>
       <c r="G24" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H24" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B25" t="s">
         <v>124</v>
@@ -5753,7 +5756,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B26" t="s">
         <v>124</v>
@@ -5767,7 +5770,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B27" t="s">
         <v>124</v>
@@ -5781,21 +5784,21 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B28" t="s">
         <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H28" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B29" t="s">
         <v>124</v>
@@ -5809,7 +5812,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B30" t="s">
         <v>124</v>
@@ -5823,22 +5826,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
+        <v>349</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>350</v>
+      </c>
+      <c r="D31" t="s">
+        <v>351</v>
+      </c>
+      <c r="E31" t="s">
+        <v>352</v>
+      </c>
+      <c r="F31" t="s">
         <v>353</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>354</v>
-      </c>
-      <c r="D31" t="s">
-        <v>355</v>
-      </c>
-      <c r="E31" t="s">
-        <v>356</v>
-      </c>
-      <c r="F31" t="s">
-        <v>357</v>
       </c>
       <c r="H31" t="str">
         <f>C31</f>
@@ -5847,36 +5850,36 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B32" t="s">
         <v>124</v>
       </c>
       <c r="G32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H32" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
+        <v>361</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>362</v>
+      </c>
+      <c r="D33" t="s">
+        <v>363</v>
+      </c>
+      <c r="E33" t="s">
+        <v>364</v>
+      </c>
+      <c r="F33" t="s">
         <v>365</v>
-      </c>
-      <c r="B33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>366</v>
-      </c>
-      <c r="D33" t="s">
-        <v>367</v>
-      </c>
-      <c r="E33" t="s">
-        <v>368</v>
-      </c>
-      <c r="F33" t="s">
-        <v>369</v>
       </c>
       <c r="H33" t="str">
         <f>F33</f>
@@ -5885,22 +5888,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="D34" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E34" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F34" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H34" t="str">
         <f>E34</f>
@@ -5909,36 +5912,36 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B35" t="s">
         <v>124</v>
       </c>
       <c r="G35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H35" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
+        <v>389</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>390</v>
+      </c>
+      <c r="D36" t="s">
+        <v>391</v>
+      </c>
+      <c r="E36" t="s">
+        <v>392</v>
+      </c>
+      <c r="F36" t="s">
         <v>393</v>
-      </c>
-      <c r="B36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" t="s">
-        <v>394</v>
-      </c>
-      <c r="D36" t="s">
-        <v>395</v>
-      </c>
-      <c r="E36" t="s">
-        <v>396</v>
-      </c>
-      <c r="F36" t="s">
-        <v>397</v>
       </c>
       <c r="H36" t="str">
         <f>F36</f>
@@ -5947,36 +5950,36 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B37" t="s">
         <v>124</v>
       </c>
       <c r="G37" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H37" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
+        <v>397</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>398</v>
+      </c>
+      <c r="D38" t="s">
+        <v>399</v>
+      </c>
+      <c r="E38" t="s">
+        <v>400</v>
+      </c>
+      <c r="F38" t="s">
         <v>401</v>
-      </c>
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
-        <v>402</v>
-      </c>
-      <c r="D38" t="s">
-        <v>403</v>
-      </c>
-      <c r="E38" t="s">
-        <v>404</v>
-      </c>
-      <c r="F38" t="s">
-        <v>405</v>
       </c>
       <c r="H38" t="str">
         <f>C38</f>
@@ -6079,21 +6082,21 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>413</v>
       </c>
       <c r="B4" t="s">
         <v>124</v>
       </c>
       <c r="G4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5" t="s">
         <v>124</v>
@@ -6107,36 +6110,36 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
         <v>124</v>
       </c>
       <c r="G6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H6" t="s">
         <v>234</v>
-      </c>
-      <c r="H6" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
         <v>252</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>254</v>
       </c>
-      <c r="D7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>255</v>
-      </c>
-      <c r="F7" t="s">
-        <v>256</v>
       </c>
       <c r="H7" t="str">
         <f>D7</f>
@@ -6145,36 +6148,36 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>411</v>
       </c>
       <c r="B8" t="s">
         <v>124</v>
       </c>
       <c r="G8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" t="s">
         <v>259</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>260</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>261</v>
-      </c>
-      <c r="E9" t="s">
-        <v>262</v>
-      </c>
-      <c r="F9" t="s">
-        <v>263</v>
       </c>
       <c r="H9" t="str">
         <f>C9</f>
@@ -6183,22 +6186,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" t="s">
         <v>274</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>275</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>276</v>
-      </c>
-      <c r="E10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" t="s">
-        <v>278</v>
       </c>
       <c r="H10" t="str">
         <f>F10</f>
@@ -6207,22 +6210,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>282</v>
+      </c>
+      <c r="D11" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" t="s">
         <v>284</v>
       </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>285</v>
-      </c>
-      <c r="D11" t="s">
-        <v>286</v>
-      </c>
-      <c r="E11" t="s">
-        <v>287</v>
-      </c>
-      <c r="F11" t="s">
-        <v>288</v>
       </c>
       <c r="H11" t="str">
         <f>C11</f>
@@ -6231,22 +6234,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D12" t="s">
+        <v>315</v>
+      </c>
+      <c r="E12" t="s">
+        <v>316</v>
+      </c>
+      <c r="F12" t="s">
         <v>317</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>318</v>
-      </c>
-      <c r="D12" t="s">
-        <v>319</v>
-      </c>
-      <c r="E12" t="s">
-        <v>320</v>
-      </c>
-      <c r="F12" t="s">
-        <v>321</v>
       </c>
       <c r="H12" t="str">
         <f>D12</f>
@@ -6255,22 +6258,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D13" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E13" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F13" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H13" t="str">
         <f>D13</f>
@@ -6279,7 +6282,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B14" t="s">
         <v>124</v>
@@ -6288,27 +6291,27 @@
         <v>124</v>
       </c>
       <c r="H14" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>331</v>
+      </c>
+      <c r="D15" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" t="s">
+        <v>333</v>
+      </c>
+      <c r="F15" t="s">
         <v>334</v>
-      </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>335</v>
-      </c>
-      <c r="D15" t="s">
-        <v>336</v>
-      </c>
-      <c r="E15" t="s">
-        <v>337</v>
-      </c>
-      <c r="F15" t="s">
-        <v>338</v>
       </c>
       <c r="H15" t="str">
         <f>C15</f>
@@ -6317,7 +6320,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
         <v>124</v>
@@ -6331,22 +6334,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>379</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>380</v>
+      </c>
+      <c r="D17" t="s">
+        <v>381</v>
+      </c>
+      <c r="E17" t="s">
+        <v>382</v>
+      </c>
+      <c r="F17" t="s">
         <v>383</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>384</v>
-      </c>
-      <c r="D17" t="s">
-        <v>385</v>
-      </c>
-      <c r="E17" t="s">
-        <v>386</v>
-      </c>
-      <c r="F17" t="s">
-        <v>387</v>
       </c>
       <c r="H17" t="str">
         <f>F17</f>
@@ -6355,22 +6358,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" t="s">
+        <v>386</v>
+      </c>
+      <c r="E18" t="s">
+        <v>387</v>
+      </c>
+      <c r="F18" t="s">
         <v>388</v>
-      </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>389</v>
-      </c>
-      <c r="D18" t="s">
-        <v>390</v>
-      </c>
-      <c r="E18" t="s">
-        <v>391</v>
-      </c>
-      <c r="F18" t="s">
-        <v>392</v>
       </c>
       <c r="H18" t="str">
         <f>C18</f>
@@ -6379,7 +6382,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B19" t="s">
         <v>124</v>
@@ -6545,7 +6548,7 @@
         <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H6" t="str">
         <f>E6</f>
@@ -6890,22 +6893,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
         <v>246</v>
       </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>247</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>248</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>249</v>
-      </c>
-      <c r="F21" t="s">
-        <v>250</v>
       </c>
       <c r="H21" t="str">
         <f>C21</f>
@@ -6914,22 +6917,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" t="s">
         <v>264</v>
       </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>265</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>266</v>
-      </c>
-      <c r="E22" t="s">
-        <v>267</v>
-      </c>
-      <c r="F22" t="s">
-        <v>268</v>
       </c>
       <c r="H22" t="str">
         <f>C22</f>
@@ -6938,22 +6941,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
+        <v>366</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>367</v>
+      </c>
+      <c r="D23" t="s">
+        <v>368</v>
+      </c>
+      <c r="E23" t="s">
+        <v>369</v>
+      </c>
+      <c r="F23" t="s">
         <v>370</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>371</v>
-      </c>
-      <c r="D23" t="s">
-        <v>372</v>
-      </c>
-      <c r="E23" t="s">
-        <v>373</v>
-      </c>
-      <c r="F23" t="s">
-        <v>374</v>
       </c>
       <c r="H23" t="str">
         <f>D23</f>
@@ -6962,7 +6965,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B24" t="s">
         <v>124</v>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93574C4-D48B-4DAE-9FFF-215404D14D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F60C1DC-9D1B-413E-BE10-A86B92460DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="414">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -1991,10 +1991,6 @@
     <rPh sb="38" eb="40">
       <t>ジキ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>chioce</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4585,7 +4581,7 @@
         <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" t="str">
@@ -5093,22 +5089,22 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>223</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>224</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>225</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>226</v>
-      </c>
-      <c r="F5" t="s">
-        <v>227</v>
       </c>
       <c r="H5" t="str">
         <f>F5</f>
@@ -5117,22 +5113,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" t="s">
         <v>289</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>290</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>291</v>
-      </c>
-      <c r="F6" t="s">
-        <v>292</v>
       </c>
       <c r="H6" t="str">
         <f>C6</f>
@@ -5141,22 +5137,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>318</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>319</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>320</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>321</v>
-      </c>
-      <c r="F7" t="s">
-        <v>322</v>
       </c>
       <c r="H7" t="str">
         <f>F7</f>
@@ -5165,7 +5161,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -5189,7 +5185,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B9" t="s">
         <v>124</v>
@@ -5198,27 +5194,27 @@
         <v>194</v>
       </c>
       <c r="H9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>342</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>343</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" t="s">
         <v>345</v>
-      </c>
-      <c r="F10" t="s">
-        <v>346</v>
       </c>
       <c r="H10" t="str">
         <f>E10</f>
@@ -5227,19 +5223,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>353</v>
+      </c>
+      <c r="B11" t="s">
         <v>354</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>355</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>356</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>357</v>
-      </c>
-      <c r="E11" t="s">
-        <v>358</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
@@ -5329,7 +5325,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D3" t="s">
         <v>185</v>
@@ -5417,19 +5413,19 @@
         <v>212</v>
       </c>
       <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
         <v>213</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>214</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>215</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>216</v>
-      </c>
-      <c r="F8" t="s">
-        <v>217</v>
       </c>
       <c r="H8" t="str">
         <f>F8</f>
@@ -5438,22 +5434,22 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>218</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>219</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>220</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>221</v>
-      </c>
-      <c r="F9" t="s">
-        <v>222</v>
       </c>
       <c r="H9" t="str">
         <f>F9</f>
@@ -5462,7 +5458,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
         <v>124</v>
@@ -5476,7 +5472,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11" t="s">
         <v>124</v>
@@ -5485,12 +5481,12 @@
         <v>194</v>
       </c>
       <c r="H11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B12" t="s">
         <v>124</v>
@@ -5499,27 +5495,27 @@
         <v>194</v>
       </c>
       <c r="H12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
         <v>240</v>
       </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>241</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>242</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>243</v>
-      </c>
-      <c r="F13" t="s">
-        <v>244</v>
       </c>
       <c r="H13" t="str">
         <f>F13</f>
@@ -5528,22 +5524,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
         <v>235</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>236</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>237</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>238</v>
-      </c>
-      <c r="F14" t="s">
-        <v>239</v>
       </c>
       <c r="H14" t="str">
         <f>F14</f>
@@ -5552,36 +5548,36 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B15" t="s">
         <v>124</v>
       </c>
       <c r="G15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
         <v>267</v>
       </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>268</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>269</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>270</v>
-      </c>
-      <c r="F16" t="s">
-        <v>271</v>
       </c>
       <c r="H16" t="str">
         <f>E16</f>
@@ -5590,22 +5586,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
         <v>277</v>
       </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>278</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>279</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>280</v>
-      </c>
-      <c r="F17" t="s">
-        <v>281</v>
       </c>
       <c r="H17" t="str">
         <f>D17</f>
@@ -5614,50 +5610,50 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B18" t="s">
         <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B19" t="s">
         <v>124</v>
       </c>
       <c r="G19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D20" t="s">
         <v>294</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>295</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>296</v>
-      </c>
-      <c r="F20" t="s">
-        <v>297</v>
       </c>
       <c r="H20" t="str">
         <f>D20</f>
@@ -5666,22 +5662,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>297</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D21" t="s">
+        <v>300</v>
+      </c>
+      <c r="E21" t="s">
         <v>298</v>
       </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>300</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>301</v>
-      </c>
-      <c r="E21" t="s">
-        <v>299</v>
-      </c>
-      <c r="F21" t="s">
-        <v>302</v>
       </c>
       <c r="H21" t="str">
         <f>E21</f>
@@ -5690,22 +5686,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>306</v>
+      </c>
+      <c r="D22" t="s">
         <v>303</v>
       </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>307</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>304</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>305</v>
-      </c>
-      <c r="F22" t="s">
-        <v>306</v>
       </c>
       <c r="H22" t="str">
         <f>D22</f>
@@ -5714,35 +5710,35 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B23" t="s">
         <v>124</v>
       </c>
       <c r="G23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B24" t="s">
         <v>124</v>
       </c>
       <c r="G24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B25" t="s">
         <v>124</v>
@@ -5756,7 +5752,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B26" t="s">
         <v>124</v>
@@ -5770,7 +5766,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B27" t="s">
         <v>124</v>
@@ -5784,21 +5780,21 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B28" t="s">
         <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B29" t="s">
         <v>124</v>
@@ -5812,7 +5808,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B30" t="s">
         <v>124</v>
@@ -5826,22 +5822,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
+        <v>348</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
         <v>349</v>
       </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>350</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>351</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>352</v>
-      </c>
-      <c r="F31" t="s">
-        <v>353</v>
       </c>
       <c r="H31" t="str">
         <f>C31</f>
@@ -5850,36 +5846,36 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B32" t="s">
         <v>124</v>
       </c>
       <c r="G32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
+        <v>360</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
         <v>361</v>
       </c>
-      <c r="B33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>362</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>363</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>364</v>
-      </c>
-      <c r="F33" t="s">
-        <v>365</v>
       </c>
       <c r="H33" t="str">
         <f>F33</f>
@@ -5888,22 +5884,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>370</v>
+      </c>
+      <c r="D34" t="s">
         <v>371</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>372</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>373</v>
-      </c>
-      <c r="F34" t="s">
-        <v>374</v>
       </c>
       <c r="H34" t="str">
         <f>E34</f>
@@ -5912,7 +5908,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s">
         <v>124</v>
@@ -5921,27 +5917,27 @@
         <v>194</v>
       </c>
       <c r="H35" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
+        <v>388</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
         <v>389</v>
       </c>
-      <c r="B36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>390</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>391</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>392</v>
-      </c>
-      <c r="F36" t="s">
-        <v>393</v>
       </c>
       <c r="H36" t="str">
         <f>F36</f>
@@ -5950,7 +5946,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B37" t="s">
         <v>124</v>
@@ -5959,27 +5955,27 @@
         <v>194</v>
       </c>
       <c r="H37" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
+        <v>396</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
         <v>397</v>
       </c>
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>398</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>399</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>400</v>
-      </c>
-      <c r="F38" t="s">
-        <v>401</v>
       </c>
       <c r="H38" t="str">
         <f>C38</f>
@@ -6082,7 +6078,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B4" t="s">
         <v>124</v>
@@ -6110,36 +6106,36 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
         <v>124</v>
       </c>
       <c r="G6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6" t="s">
         <v>233</v>
-      </c>
-      <c r="H6" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D7" t="s">
         <v>251</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>253</v>
       </c>
-      <c r="D7" t="s">
-        <v>252</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>254</v>
-      </c>
-      <c r="F7" t="s">
-        <v>255</v>
       </c>
       <c r="H7" t="str">
         <f>D7</f>
@@ -6148,7 +6144,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B8" t="s">
         <v>124</v>
@@ -6157,27 +6153,27 @@
         <v>194</v>
       </c>
       <c r="H8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>257</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>258</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>259</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>260</v>
-      </c>
-      <c r="F9" t="s">
-        <v>261</v>
       </c>
       <c r="H9" t="str">
         <f>C9</f>
@@ -6186,22 +6182,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>272</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>273</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>274</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>275</v>
-      </c>
-      <c r="F10" t="s">
-        <v>276</v>
       </c>
       <c r="H10" t="str">
         <f>F10</f>
@@ -6210,22 +6206,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D11" t="s">
         <v>282</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>283</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>284</v>
-      </c>
-      <c r="F11" t="s">
-        <v>285</v>
       </c>
       <c r="H11" t="str">
         <f>C11</f>
@@ -6234,22 +6230,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>313</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>314</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>315</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>316</v>
-      </c>
-      <c r="F12" t="s">
-        <v>317</v>
       </c>
       <c r="H12" t="str">
         <f>D12</f>
@@ -6258,22 +6254,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" t="s">
         <v>324</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>325</v>
       </c>
-      <c r="E13" t="s">
-        <v>326</v>
-      </c>
       <c r="F13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H13" t="str">
         <f>D13</f>
@@ -6282,36 +6278,36 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B14" t="s">
         <v>124</v>
       </c>
       <c r="G14" t="s">
-        <v>124</v>
+        <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
         <v>330</v>
       </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>331</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>332</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>333</v>
-      </c>
-      <c r="F15" t="s">
-        <v>334</v>
       </c>
       <c r="H15" t="str">
         <f>C15</f>
@@ -6320,7 +6316,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
         <v>124</v>
@@ -6334,22 +6330,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
         <v>379</v>
       </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>380</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>381</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>382</v>
-      </c>
-      <c r="F17" t="s">
-        <v>383</v>
       </c>
       <c r="H17" t="str">
         <f>F17</f>
@@ -6358,22 +6354,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>383</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
         <v>384</v>
       </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>385</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>386</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>387</v>
-      </c>
-      <c r="F18" t="s">
-        <v>388</v>
       </c>
       <c r="H18" t="str">
         <f>C18</f>
@@ -6382,7 +6378,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B19" t="s">
         <v>124</v>
@@ -6893,22 +6889,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
         <v>245</v>
       </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>246</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>247</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>248</v>
-      </c>
-      <c r="F21" t="s">
-        <v>249</v>
       </c>
       <c r="H21" t="str">
         <f>C21</f>
@@ -6917,22 +6913,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
         <v>262</v>
       </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>263</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>264</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>265</v>
-      </c>
-      <c r="F22" t="s">
-        <v>266</v>
       </c>
       <c r="H22" t="str">
         <f>C22</f>
@@ -6941,22 +6937,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
+        <v>365</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
         <v>366</v>
       </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>367</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>368</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>369</v>
-      </c>
-      <c r="F23" t="s">
-        <v>370</v>
       </c>
       <c r="H23" t="str">
         <f>D23</f>
@@ -6965,7 +6961,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B24" t="s">
         <v>124</v>

--- a/questions/question.xlsx
+++ b/questions/question.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csryou\Desktop\quiz-project\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F60C1DC-9D1B-413E-BE10-A86B92460DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF6AFA4-4EDE-4FB4-8D30-303ECA3EBBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{C2D6912E-C08B-421F-A500-3E2A6D20402B}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="413">
   <si>
     <t>問題</t>
     <rPh sb="0" eb="2">
@@ -2230,13 +2230,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>星野カービィーシリーズ</t>
-    <rPh sb="0" eb="2">
-      <t>ホシノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メトロシリーズ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -3344,10 +3337,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>chhoice</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>きのこ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -4093,6 +4082,13 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星のカービィーシリーズ</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4581,7 +4577,7 @@
         <v>97</v>
       </c>
       <c r="F2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" t="str">
@@ -5113,22 +5109,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" t="s">
         <v>288</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>287</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>289</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>290</v>
-      </c>
-      <c r="F6" t="s">
-        <v>291</v>
       </c>
       <c r="H6" t="str">
         <f>C6</f>
@@ -5137,22 +5133,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>317</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>318</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>319</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>320</v>
-      </c>
-      <c r="F7" t="s">
-        <v>321</v>
       </c>
       <c r="H7" t="str">
         <f>F7</f>
@@ -5161,7 +5157,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -5185,7 +5181,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B9" t="s">
         <v>124</v>
@@ -5194,27 +5190,27 @@
         <v>194</v>
       </c>
       <c r="H9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>341</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>342</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" t="s">
         <v>344</v>
-      </c>
-      <c r="F10" t="s">
-        <v>345</v>
       </c>
       <c r="H10" t="str">
         <f>E10</f>
@@ -5223,19 +5219,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
+        <v>352</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
         <v>353</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>354</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>355</v>
-      </c>
-      <c r="D11" t="s">
-        <v>356</v>
-      </c>
-      <c r="E11" t="s">
-        <v>357</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
@@ -5325,7 +5321,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D3" t="s">
         <v>185</v>
@@ -5472,7 +5468,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B11" t="s">
         <v>124</v>
@@ -5512,10 +5508,10 @@
         <v>241</v>
       </c>
       <c r="E13" t="s">
+        <v>412</v>
+      </c>
+      <c r="F13" t="s">
         <v>242</v>
-      </c>
-      <c r="F13" t="s">
-        <v>243</v>
       </c>
       <c r="H13" t="str">
         <f>F13</f>
@@ -5548,36 +5544,36 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B15" t="s">
         <v>124</v>
       </c>
       <c r="G15" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>265</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
         <v>266</v>
       </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>267</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>268</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>269</v>
-      </c>
-      <c r="F16" t="s">
-        <v>270</v>
       </c>
       <c r="H16" t="str">
         <f>E16</f>
@@ -5586,22 +5582,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
         <v>276</v>
       </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>277</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>278</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>279</v>
-      </c>
-      <c r="F17" t="s">
-        <v>280</v>
       </c>
       <c r="H17" t="str">
         <f>D17</f>
@@ -5610,7 +5606,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B18" t="s">
         <v>124</v>
@@ -5619,12 +5615,12 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B19" t="s">
         <v>124</v>
@@ -5633,27 +5629,27 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>292</v>
+      </c>
+      <c r="D20" t="s">
         <v>293</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>294</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>295</v>
-      </c>
-      <c r="F20" t="s">
-        <v>296</v>
       </c>
       <c r="H20" t="str">
         <f>D20</f>
@@ -5662,22 +5658,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>296</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D21" t="s">
+        <v>299</v>
+      </c>
+      <c r="E21" t="s">
         <v>297</v>
       </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>299</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>300</v>
-      </c>
-      <c r="E21" t="s">
-        <v>298</v>
-      </c>
-      <c r="F21" t="s">
-        <v>301</v>
       </c>
       <c r="H21" t="str">
         <f>E21</f>
@@ -5686,22 +5682,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>301</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D22" t="s">
         <v>302</v>
       </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>306</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>303</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>304</v>
-      </c>
-      <c r="F22" t="s">
-        <v>305</v>
       </c>
       <c r="H22" t="str">
         <f>D22</f>
@@ -5710,35 +5706,35 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B23" t="s">
         <v>124</v>
       </c>
       <c r="G23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B24" t="s">
         <v>124</v>
       </c>
       <c r="G24" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B25" t="s">
         <v>124</v>
@@ -5752,7 +5748,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B26" t="s">
         <v>124</v>
@@ -5766,7 +5762,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B27" t="s">
         <v>124</v>
@@ -5780,7 +5776,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s">
         <v>124</v>
@@ -5789,12 +5785,12 @@
         <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B29" t="s">
         <v>124</v>
@@ -5808,7 +5804,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B30" t="s">
         <v>124</v>
@@ -5822,22 +5818,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
+        <v>347</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
         <v>348</v>
       </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>349</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>350</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>351</v>
-      </c>
-      <c r="F31" t="s">
-        <v>352</v>
       </c>
       <c r="H31" t="str">
         <f>C31</f>
@@ -5846,36 +5842,36 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B32" t="s">
         <v>124</v>
       </c>
       <c r="G32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H32" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
+        <v>358</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>359</v>
+      </c>
+      <c r="D33" t="s">
         <v>360</v>
       </c>
-      <c r="B33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
         <v>361</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>362</v>
-      </c>
-      <c r="E33" t="s">
-        <v>363</v>
-      </c>
-      <c r="F33" t="s">
-        <v>364</v>
       </c>
       <c r="H33" t="str">
         <f>F33</f>
@@ -5884,22 +5880,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>368</v>
+      </c>
+      <c r="D34" t="s">
+        <v>369</v>
+      </c>
+      <c r="E34" t="s">
         <v>370</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>371</v>
-      </c>
-      <c r="E34" t="s">
-        <v>372</v>
-      </c>
-      <c r="F34" t="s">
-        <v>373</v>
       </c>
       <c r="H34" t="str">
         <f>E34</f>
@@ -5908,7 +5904,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s">
         <v>124</v>
@@ -5917,27 +5913,27 @@
         <v>194</v>
       </c>
       <c r="H35" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
+        <v>386</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>387</v>
+      </c>
+      <c r="D36" t="s">
         <v>388</v>
       </c>
-      <c r="B36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="E36" t="s">
         <v>389</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>390</v>
-      </c>
-      <c r="E36" t="s">
-        <v>391</v>
-      </c>
-      <c r="F36" t="s">
-        <v>392</v>
       </c>
       <c r="H36" t="str">
         <f>F36</f>
@@ -5946,7 +5942,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B37" t="s">
         <v>124</v>
@@ -5955,27 +5951,27 @@
         <v>194</v>
       </c>
       <c r="H37" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
+        <v>394</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>395</v>
+      </c>
+      <c r="D38" t="s">
         <v>396</v>
       </c>
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="E38" t="s">
         <v>397</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>398</v>
-      </c>
-      <c r="E38" t="s">
-        <v>399</v>
-      </c>
-      <c r="F38" t="s">
-        <v>400</v>
       </c>
       <c r="H38" t="str">
         <f>C38</f>
@@ -6078,7 +6074,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B4" t="s">
         <v>124</v>
@@ -6120,22 +6116,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" t="s">
         <v>250</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>252</v>
       </c>
-      <c r="D7" t="s">
-        <v>251</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>253</v>
-      </c>
-      <c r="F7" t="s">
-        <v>254</v>
       </c>
       <c r="H7" t="str">
         <f>D7</f>
@@ -6144,7 +6140,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B8" t="s">
         <v>124</v>
@@ -6153,27 +6149,27 @@
         <v>194</v>
       </c>
       <c r="H8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>256</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>257</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>258</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>259</v>
-      </c>
-      <c r="F9" t="s">
-        <v>260</v>
       </c>
       <c r="H9" t="str">
         <f>C9</f>
@@ -6182,22 +6178,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>271</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>272</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>273</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>274</v>
-      </c>
-      <c r="F10" t="s">
-        <v>275</v>
       </c>
       <c r="H10" t="str">
         <f>F10</f>
@@ -6206,22 +6202,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" t="s">
         <v>281</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>282</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>283</v>
-      </c>
-      <c r="F11" t="s">
-        <v>284</v>
       </c>
       <c r="H11" t="str">
         <f>C11</f>
@@ -6230,22 +6226,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>312</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>313</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>314</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>315</v>
-      </c>
-      <c r="F12" t="s">
-        <v>316</v>
       </c>
       <c r="H12" t="str">
         <f>D12</f>
@@ -6254,22 +6250,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D13" t="s">
         <v>323</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>324</v>
       </c>
-      <c r="E13" t="s">
-        <v>325</v>
-      </c>
       <c r="F13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H13" t="str">
         <f>D13</f>
@@ -6278,7 +6274,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B14" t="s">
         <v>124</v>
@@ -6287,27 +6283,27 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>328</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
         <v>329</v>
       </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>330</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>331</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>332</v>
-      </c>
-      <c r="F15" t="s">
-        <v>333</v>
       </c>
       <c r="H15" t="str">
         <f>C15</f>
@@ -6316,7 +6312,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B16" t="s">
         <v>124</v>
@@ -6330,22 +6326,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>377</v>
+      </c>
+      <c r="D17" t="s">
         <v>378</v>
       </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>379</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>380</v>
-      </c>
-      <c r="E17" t="s">
-        <v>381</v>
-      </c>
-      <c r="F17" t="s">
-        <v>382</v>
       </c>
       <c r="H17" t="str">
         <f>F17</f>
@@ -6354,22 +6350,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>381</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>382</v>
+      </c>
+      <c r="D18" t="s">
         <v>383</v>
       </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>384</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>385</v>
-      </c>
-      <c r="E18" t="s">
-        <v>386</v>
-      </c>
-      <c r="F18" t="s">
-        <v>387</v>
       </c>
       <c r="H18" t="str">
         <f>C18</f>
@@ -6378,7 +6374,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B19" t="s">
         <v>124</v>
@@ -6889,22 +6885,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
         <v>244</v>
       </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>245</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>246</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>247</v>
-      </c>
-      <c r="F21" t="s">
-        <v>248</v>
       </c>
       <c r="H21" t="str">
         <f>C21</f>
@@ -6913,22 +6909,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
+        <v>260</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
         <v>261</v>
       </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>262</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>263</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>264</v>
-      </c>
-      <c r="F22" t="s">
-        <v>265</v>
       </c>
       <c r="H22" t="str">
         <f>C22</f>
@@ -6937,22 +6933,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
+        <v>363</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>364</v>
+      </c>
+      <c r="D23" t="s">
         <v>365</v>
       </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>366</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>367</v>
-      </c>
-      <c r="E23" t="s">
-        <v>368</v>
-      </c>
-      <c r="F23" t="s">
-        <v>369</v>
       </c>
       <c r="H23" t="str">
         <f>D23</f>
@@ -6961,7 +6957,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B24" t="s">
         <v>124</v>
